--- a/data/umr/Resumen UMR Junio 2026.xlsx
+++ b/data/umr/Resumen UMR Junio 2026.xlsx
@@ -45787,13 +45787,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83762C89-4068-4436-8B2C-8CE31090944D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CDF204E-0F69-48BF-B55D-4AA794A69F79}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E62D660-79B4-4FB3-9062-DA3FB141621A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015359CB-7DF5-43D5-A22D-803017E8B905}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03CA00B3-638D-49D3-82DE-34F01981DECA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7581C8-F14F-44A7-BCB9-28C305E1109E}"/>
 </file>
--- a/data/umr/Resumen UMR Junio 2026.xlsx
+++ b/data/umr/Resumen UMR Junio 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC15471-B973-4801-83DB-DC0C980A4BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6FD30B-F375-45DA-8AE3-7D69E6725542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4620,6 +4620,12 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="86" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="86" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4737,12 +4743,6 @@
     </xf>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="59" borderId="86" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="60" borderId="86" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -5754,37 +5754,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="346" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="346"/>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
-      <c r="I1" s="346"/>
-      <c r="J1" s="346"/>
-      <c r="K1" s="346"/>
-      <c r="L1" s="346"/>
-      <c r="M1" s="346"/>
-      <c r="N1" s="346"/>
-      <c r="O1" s="346"/>
-      <c r="P1" s="346"/>
-      <c r="Q1" s="346"/>
-      <c r="R1" s="346"/>
-      <c r="S1" s="346"/>
-      <c r="T1" s="346"/>
-      <c r="U1" s="346"/>
-      <c r="V1" s="346"/>
-      <c r="W1" s="346"/>
-      <c r="X1" s="346"/>
-      <c r="Y1" s="346"/>
-      <c r="Z1" s="346"/>
-      <c r="AA1" s="346"/>
-      <c r="AB1" s="346"/>
-      <c r="AC1" s="346"/>
+      <c r="A1" s="348" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="348"/>
+      <c r="C1" s="348"/>
+      <c r="D1" s="348"/>
+      <c r="E1" s="348"/>
+      <c r="F1" s="348"/>
+      <c r="G1" s="348"/>
+      <c r="H1" s="348"/>
+      <c r="I1" s="348"/>
+      <c r="J1" s="348"/>
+      <c r="K1" s="348"/>
+      <c r="L1" s="348"/>
+      <c r="M1" s="348"/>
+      <c r="N1" s="348"/>
+      <c r="O1" s="348"/>
+      <c r="P1" s="348"/>
+      <c r="Q1" s="348"/>
+      <c r="R1" s="348"/>
+      <c r="S1" s="348"/>
+      <c r="T1" s="348"/>
+      <c r="U1" s="348"/>
+      <c r="V1" s="348"/>
+      <c r="W1" s="348"/>
+      <c r="X1" s="348"/>
+      <c r="Y1" s="348"/>
+      <c r="Z1" s="348"/>
+      <c r="AA1" s="348"/>
+      <c r="AB1" s="348"/>
+      <c r="AC1" s="348"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -6158,7 +6158,9 @@
       <c r="AD5" s="225">
         <v>2140380</v>
       </c>
-      <c r="AE5" s="225"/>
+      <c r="AE5" s="225">
+        <v>2140583</v>
+      </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -6251,7 +6253,9 @@
       <c r="AD6" s="225">
         <v>2104374</v>
       </c>
-      <c r="AE6" s="225"/>
+      <c r="AE6" s="225">
+        <v>2104662</v>
+      </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
@@ -6344,7 +6348,9 @@
       <c r="AD7" s="225">
         <v>2182931</v>
       </c>
-      <c r="AE7" s="225"/>
+      <c r="AE7" s="225">
+        <v>2183449</v>
+      </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -6437,7 +6443,9 @@
       <c r="AD8" s="225">
         <v>2186275</v>
       </c>
-      <c r="AE8" s="225"/>
+      <c r="AE8" s="225">
+        <v>2186728</v>
+      </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
@@ -6530,7 +6538,9 @@
       <c r="AD9" s="225">
         <v>2102077</v>
       </c>
-      <c r="AE9" s="225"/>
+      <c r="AE9" s="225">
+        <v>2102571</v>
+      </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
@@ -6623,7 +6633,9 @@
       <c r="AD10" s="225">
         <v>2210979</v>
       </c>
-      <c r="AE10" s="225"/>
+      <c r="AE10" s="225">
+        <v>2211229</v>
+      </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -6716,7 +6728,9 @@
       <c r="AD11" s="225">
         <v>2247405</v>
       </c>
-      <c r="AE11" s="225"/>
+      <c r="AE11" s="225">
+        <v>2247616</v>
+      </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
@@ -6809,7 +6823,9 @@
       <c r="AD12" s="225">
         <v>2145263</v>
       </c>
-      <c r="AE12" s="225"/>
+      <c r="AE12" s="225">
+        <v>2145866</v>
+      </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
@@ -6902,7 +6918,9 @@
       <c r="AD13" s="225">
         <v>2130691</v>
       </c>
-      <c r="AE13" s="225"/>
+      <c r="AE13" s="225">
+        <v>2131251</v>
+      </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
@@ -6995,7 +7013,9 @@
       <c r="AD14" s="225">
         <v>2199262</v>
       </c>
-      <c r="AE14" s="225"/>
+      <c r="AE14" s="225">
+        <v>2199713</v>
+      </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
@@ -7088,7 +7108,9 @@
       <c r="AD15" s="225">
         <v>2225903</v>
       </c>
-      <c r="AE15" s="225"/>
+      <c r="AE15" s="225">
+        <v>2226219</v>
+      </c>
       <c r="AH15" t="s">
         <v>144</v>
       </c>
@@ -7184,7 +7206,9 @@
       <c r="AD16" s="225">
         <v>2071591</v>
       </c>
-      <c r="AE16" s="225"/>
+      <c r="AE16" s="225">
+        <v>2071670</v>
+      </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
@@ -7277,7 +7301,9 @@
       <c r="AD17" s="225">
         <v>2176763</v>
       </c>
-      <c r="AE17" s="225"/>
+      <c r="AE17" s="225">
+        <v>2177013</v>
+      </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
@@ -7370,7 +7396,9 @@
       <c r="AD18" s="225">
         <v>2148475</v>
       </c>
-      <c r="AE18" s="225"/>
+      <c r="AE18" s="225">
+        <v>2148927</v>
+      </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
@@ -7463,7 +7491,9 @@
       <c r="AD19" s="225">
         <v>2236752</v>
       </c>
-      <c r="AE19" s="225"/>
+      <c r="AE19" s="225">
+        <v>2236752</v>
+      </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
@@ -7556,7 +7586,9 @@
       <c r="AD20" s="225">
         <v>2205883</v>
       </c>
-      <c r="AE20" s="225"/>
+      <c r="AE20" s="225">
+        <v>2206064</v>
+      </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
@@ -7649,7 +7681,9 @@
       <c r="AD21" s="225">
         <v>2210908</v>
       </c>
-      <c r="AE21" s="225"/>
+      <c r="AE21" s="225">
+        <v>2210989</v>
+      </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -7742,7 +7776,9 @@
       <c r="AD22" s="225">
         <v>2138972</v>
       </c>
-      <c r="AE22" s="225"/>
+      <c r="AE22" s="225">
+        <v>2139474</v>
+      </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
@@ -7835,7 +7871,9 @@
       <c r="AD23" s="225">
         <v>2170707</v>
       </c>
-      <c r="AE23" s="225"/>
+      <c r="AE23" s="225">
+        <v>2171200</v>
+      </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
@@ -7928,7 +7966,9 @@
       <c r="AD24" s="225">
         <v>2209884</v>
       </c>
-      <c r="AE24" s="225"/>
+      <c r="AE24" s="225">
+        <v>2210401</v>
+      </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
@@ -8021,7 +8061,9 @@
       <c r="AD25" s="225">
         <v>2224882</v>
       </c>
-      <c r="AE25" s="225"/>
+      <c r="AE25" s="225">
+        <v>2225226</v>
+      </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
@@ -8114,7 +8156,9 @@
       <c r="AD26" s="225">
         <v>2224455</v>
       </c>
-      <c r="AE26" s="225"/>
+      <c r="AE26" s="225">
+        <v>2225016</v>
+      </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
@@ -8207,7 +8251,9 @@
       <c r="AD27" s="225">
         <v>2191754</v>
       </c>
-      <c r="AE27" s="225"/>
+      <c r="AE27" s="225">
+        <v>2192085</v>
+      </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
@@ -8300,7 +8346,9 @@
       <c r="AD28" s="225">
         <v>2156645</v>
       </c>
-      <c r="AE28" s="225"/>
+      <c r="AE28" s="225">
+        <v>2157192</v>
+      </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
@@ -8393,7 +8441,9 @@
       <c r="AD29" s="225">
         <v>2108784</v>
       </c>
-      <c r="AE29" s="225"/>
+      <c r="AE29" s="225">
+        <v>2109034</v>
+      </c>
       <c r="AF29" s="124"/>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
@@ -8487,7 +8537,9 @@
       <c r="AD30" s="225">
         <v>1855380</v>
       </c>
-      <c r="AE30" s="225"/>
+      <c r="AE30" s="225">
+        <v>1855576</v>
+      </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
@@ -8580,7 +8632,9 @@
       <c r="AD31" s="225">
         <v>2156941</v>
       </c>
-      <c r="AE31" s="225"/>
+      <c r="AE31" s="225">
+        <v>2157501</v>
+      </c>
     </row>
     <row r="32" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
@@ -8673,7 +8727,9 @@
       <c r="AD32" s="225">
         <v>753287</v>
       </c>
-      <c r="AE32" s="225"/>
+      <c r="AE32" s="225">
+        <v>753553</v>
+      </c>
     </row>
     <row r="33" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
@@ -8766,7 +8822,9 @@
       <c r="AD33" s="225">
         <v>686861</v>
       </c>
-      <c r="AE33" s="225"/>
+      <c r="AE33" s="225">
+        <v>687293</v>
+      </c>
     </row>
     <row r="34" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
@@ -8859,7 +8917,9 @@
       <c r="AD34" s="225">
         <v>729428</v>
       </c>
-      <c r="AE34" s="225"/>
+      <c r="AE34" s="225">
+        <v>729949</v>
+      </c>
     </row>
     <row r="35" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
@@ -8952,7 +9012,9 @@
       <c r="AD35" s="225">
         <v>749373</v>
       </c>
-      <c r="AE35" s="225"/>
+      <c r="AE35" s="225">
+        <v>749626</v>
+      </c>
     </row>
     <row r="36" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
@@ -9045,7 +9107,9 @@
       <c r="AD36" s="225">
         <v>722098</v>
       </c>
-      <c r="AE36" s="225"/>
+      <c r="AE36" s="225">
+        <v>722348</v>
+      </c>
     </row>
     <row r="37" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
@@ -9138,7 +9202,9 @@
       <c r="AD37" s="225">
         <v>763369</v>
       </c>
-      <c r="AE37" s="225"/>
+      <c r="AE37" s="225">
+        <v>763756</v>
+      </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
@@ -9231,7 +9297,9 @@
       <c r="AD38" s="225">
         <v>413527</v>
       </c>
-      <c r="AE38" s="225"/>
+      <c r="AE38" s="225">
+        <v>413874</v>
+      </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
@@ -9324,7 +9392,9 @@
       <c r="AD39" s="225">
         <v>740636</v>
       </c>
-      <c r="AE39" s="225"/>
+      <c r="AE39" s="225">
+        <v>741200</v>
+      </c>
     </row>
     <row r="40" spans="1:31" s="124" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="212"/>
@@ -9448,7 +9518,9 @@
       <c r="AD41" s="225">
         <v>3675</v>
       </c>
-      <c r="AE41" s="225"/>
+      <c r="AE41" s="225">
+        <v>3675</v>
+      </c>
     </row>
     <row r="42" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="336" t="s">
@@ -9541,7 +9613,9 @@
       <c r="AD42" s="225">
         <v>2001</v>
       </c>
-      <c r="AE42" s="225"/>
+      <c r="AE42" s="225">
+        <v>2001</v>
+      </c>
     </row>
     <row r="43" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="337" t="s">
@@ -9634,7 +9708,9 @@
       <c r="AD43" s="225">
         <v>14116</v>
       </c>
-      <c r="AE43" s="225"/>
+      <c r="AE43" s="225">
+        <v>14202</v>
+      </c>
     </row>
     <row r="44" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="336" t="s">
@@ -9727,7 +9803,9 @@
       <c r="AD44" s="225">
         <v>1802</v>
       </c>
-      <c r="AE44" s="225"/>
+      <c r="AE44" s="225">
+        <v>1802</v>
+      </c>
     </row>
     <row r="45" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="337" t="s">
@@ -9820,7 +9898,9 @@
       <c r="AD45" s="225">
         <v>2123</v>
       </c>
-      <c r="AE45" s="225"/>
+      <c r="AE45" s="225">
+        <v>2123</v>
+      </c>
     </row>
     <row r="46" spans="1:31" s="124" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A46" s="212"/>
@@ -9853,37 +9933,37 @@
       <c r="AC46" s="212"/>
     </row>
     <row r="47" spans="1:31" ht="18" x14ac:dyDescent="0.25">
-      <c r="A47" s="346" t="s">
+      <c r="A47" s="348" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="346"/>
-      <c r="C47" s="346"/>
-      <c r="D47" s="346"/>
-      <c r="E47" s="346"/>
-      <c r="F47" s="346"/>
-      <c r="G47" s="346"/>
-      <c r="H47" s="346"/>
-      <c r="I47" s="346"/>
-      <c r="J47" s="346"/>
-      <c r="K47" s="346"/>
-      <c r="L47" s="346"/>
-      <c r="M47" s="346"/>
-      <c r="N47" s="346"/>
-      <c r="O47" s="346"/>
-      <c r="P47" s="346"/>
-      <c r="Q47" s="346"/>
-      <c r="R47" s="346"/>
-      <c r="S47" s="346"/>
-      <c r="T47" s="346"/>
-      <c r="U47" s="346"/>
-      <c r="V47" s="346"/>
-      <c r="W47" s="346"/>
-      <c r="X47" s="346"/>
-      <c r="Y47" s="346"/>
-      <c r="Z47" s="346"/>
-      <c r="AA47" s="346"/>
-      <c r="AB47" s="346"/>
-      <c r="AC47" s="346"/>
+      <c r="B47" s="348"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
+      <c r="G47" s="348"/>
+      <c r="H47" s="348"/>
+      <c r="I47" s="348"/>
+      <c r="J47" s="348"/>
+      <c r="K47" s="348"/>
+      <c r="L47" s="348"/>
+      <c r="M47" s="348"/>
+      <c r="N47" s="348"/>
+      <c r="O47" s="348"/>
+      <c r="P47" s="348"/>
+      <c r="Q47" s="348"/>
+      <c r="R47" s="348"/>
+      <c r="S47" s="348"/>
+      <c r="T47" s="348"/>
+      <c r="U47" s="348"/>
+      <c r="V47" s="348"/>
+      <c r="W47" s="348"/>
+      <c r="X47" s="348"/>
+      <c r="Y47" s="348"/>
+      <c r="Z47" s="348"/>
+      <c r="AA47" s="348"/>
+      <c r="AB47" s="348"/>
+      <c r="AC47" s="348"/>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="9"/>
@@ -10287,7 +10367,7 @@
       </c>
       <c r="AE51" s="12">
         <f t="shared" si="1"/>
-        <v>-2140380</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.25">
@@ -10411,7 +10491,7 @@
       </c>
       <c r="AE52" s="12">
         <f t="shared" si="3"/>
-        <v>-2104374</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.25">
@@ -10535,7 +10615,7 @@
       </c>
       <c r="AE53" s="12">
         <f t="shared" si="5"/>
-        <v>-2182931</v>
+        <v>518</v>
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.25">
@@ -10659,7 +10739,7 @@
       </c>
       <c r="AE54" s="12">
         <f t="shared" si="7"/>
-        <v>-2186275</v>
+        <v>453</v>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.25">
@@ -10783,7 +10863,7 @@
       </c>
       <c r="AE55" s="12">
         <f t="shared" si="9"/>
-        <v>-2102077</v>
+        <v>494</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.25">
@@ -10907,7 +10987,7 @@
       </c>
       <c r="AE56" s="12">
         <f t="shared" si="11"/>
-        <v>-2210979</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.25">
@@ -11031,7 +11111,7 @@
       </c>
       <c r="AE57" s="12">
         <f t="shared" si="13"/>
-        <v>-2247405</v>
+        <v>211</v>
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.25">
@@ -11155,7 +11235,7 @@
       </c>
       <c r="AE58" s="12">
         <f t="shared" si="15"/>
-        <v>-2145263</v>
+        <v>603</v>
       </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.25">
@@ -11279,7 +11359,7 @@
       </c>
       <c r="AE59" s="12">
         <f t="shared" si="17"/>
-        <v>-2130691</v>
+        <v>560</v>
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.25">
@@ -11403,7 +11483,7 @@
       </c>
       <c r="AE60" s="12">
         <f t="shared" si="19"/>
-        <v>-2199262</v>
+        <v>451</v>
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.25">
@@ -11527,7 +11607,7 @@
       </c>
       <c r="AE61" s="12">
         <f t="shared" si="21"/>
-        <v>-2225903</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.25">
@@ -11651,7 +11731,7 @@
       </c>
       <c r="AE62" s="12">
         <f t="shared" si="23"/>
-        <v>-2071591</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.25">
@@ -11775,7 +11855,7 @@
       </c>
       <c r="AE63" s="12">
         <f t="shared" si="25"/>
-        <v>-2176763</v>
+        <v>250</v>
       </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.25">
@@ -11899,7 +11979,7 @@
       </c>
       <c r="AE64" s="12">
         <f t="shared" si="27"/>
-        <v>-2148475</v>
+        <v>452</v>
       </c>
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.25">
@@ -12023,7 +12103,7 @@
       </c>
       <c r="AE65" s="12">
         <f t="shared" si="29"/>
-        <v>-2236752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:31" x14ac:dyDescent="0.25">
@@ -12147,7 +12227,7 @@
       </c>
       <c r="AE66" s="12">
         <f t="shared" si="31"/>
-        <v>-2205883</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:31" x14ac:dyDescent="0.25">
@@ -12271,7 +12351,7 @@
       </c>
       <c r="AE67" s="12">
         <f t="shared" si="33"/>
-        <v>-2210908</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:31" x14ac:dyDescent="0.25">
@@ -12395,7 +12475,7 @@
       </c>
       <c r="AE68" s="12">
         <f t="shared" si="35"/>
-        <v>-2138972</v>
+        <v>502</v>
       </c>
     </row>
     <row r="69" spans="1:31" x14ac:dyDescent="0.25">
@@ -12519,7 +12599,7 @@
       </c>
       <c r="AE69" s="12">
         <f t="shared" si="37"/>
-        <v>-2170707</v>
+        <v>493</v>
       </c>
     </row>
     <row r="70" spans="1:31" x14ac:dyDescent="0.25">
@@ -12643,7 +12723,7 @@
       </c>
       <c r="AE70" s="12">
         <f t="shared" si="39"/>
-        <v>-2209884</v>
+        <v>517</v>
       </c>
     </row>
     <row r="71" spans="1:31" x14ac:dyDescent="0.25">
@@ -12767,7 +12847,7 @@
       </c>
       <c r="AE71" s="12">
         <f t="shared" si="41"/>
-        <v>-2224882</v>
+        <v>344</v>
       </c>
     </row>
     <row r="72" spans="1:31" x14ac:dyDescent="0.25">
@@ -12891,7 +12971,7 @@
       </c>
       <c r="AE72" s="12">
         <f t="shared" si="43"/>
-        <v>-2224455</v>
+        <v>561</v>
       </c>
     </row>
     <row r="73" spans="1:31" x14ac:dyDescent="0.25">
@@ -13015,7 +13095,7 @@
       </c>
       <c r="AE73" s="12">
         <f t="shared" si="45"/>
-        <v>-2191754</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:31" x14ac:dyDescent="0.25">
@@ -13139,7 +13219,7 @@
       </c>
       <c r="AE74" s="12">
         <f t="shared" si="47"/>
-        <v>-2156645</v>
+        <v>547</v>
       </c>
     </row>
     <row r="75" spans="1:31" x14ac:dyDescent="0.25">
@@ -13263,7 +13343,7 @@
       </c>
       <c r="AE75" s="12">
         <f t="shared" si="49"/>
-        <v>-2108784</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.25">
@@ -13387,7 +13467,7 @@
       </c>
       <c r="AE76" s="12">
         <f t="shared" si="51"/>
-        <v>-1855380</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.25">
@@ -13511,7 +13591,7 @@
       </c>
       <c r="AE77" s="12">
         <f t="shared" si="53"/>
-        <v>-2156941</v>
+        <v>560</v>
       </c>
     </row>
     <row r="78" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -13635,7 +13715,7 @@
       </c>
       <c r="AE78" s="12">
         <f t="shared" si="55"/>
-        <v>-753287</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -13759,7 +13839,7 @@
       </c>
       <c r="AE79" s="12">
         <f t="shared" si="57"/>
-        <v>-686861</v>
+        <v>432</v>
       </c>
     </row>
     <row r="80" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -13883,7 +13963,7 @@
       </c>
       <c r="AE80" s="12">
         <f t="shared" si="59"/>
-        <v>-729428</v>
+        <v>521</v>
       </c>
     </row>
     <row r="81" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -14007,7 +14087,7 @@
       </c>
       <c r="AE81" s="12">
         <f t="shared" si="61"/>
-        <v>-749373</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -14131,7 +14211,7 @@
       </c>
       <c r="AE82" s="12">
         <f t="shared" si="63"/>
-        <v>-722098</v>
+        <v>250</v>
       </c>
     </row>
     <row r="83" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -14255,7 +14335,7 @@
       </c>
       <c r="AE83" s="12">
         <f t="shared" si="65"/>
-        <v>-763369</v>
+        <v>387</v>
       </c>
     </row>
     <row r="84" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -14379,7 +14459,7 @@
       </c>
       <c r="AE84" s="12">
         <f t="shared" si="67"/>
-        <v>-413527</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -14503,7 +14583,7 @@
       </c>
       <c r="AE85" s="12">
         <f t="shared" si="69"/>
-        <v>-740636</v>
+        <v>564</v>
       </c>
     </row>
     <row r="86" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -14627,7 +14707,7 @@
       </c>
       <c r="AE86" s="327">
         <f t="shared" si="71"/>
-        <v>-14116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14781,7 +14861,7 @@
       </c>
       <c r="AE88" s="16">
         <f t="shared" si="73"/>
-        <v>-63937011</v>
+        <v>12797</v>
       </c>
     </row>
     <row r="89" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -14936,7 +15016,7 @@
       </c>
       <c r="AE90" s="327">
         <f t="shared" si="78"/>
-        <v>-3675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -15052,7 +15132,7 @@
       </c>
       <c r="AE91" s="327">
         <f t="shared" ref="AE91" si="87">AE42-AD42</f>
-        <v>-2001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -15176,7 +15256,7 @@
       </c>
       <c r="AE92" s="327">
         <f t="shared" si="108"/>
-        <v>-1802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -15300,7 +15380,7 @@
       </c>
       <c r="AE93" s="327">
         <f t="shared" ref="AE93" si="116">AE45-AD45</f>
-        <v>-2123</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15437,14 +15517,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="369" t="s">
+      <c r="B2" s="371" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="369"/>
-      <c r="D2" s="370" t="s">
+      <c r="C2" s="371"/>
+      <c r="D2" s="372" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="370"/>
+      <c r="E2" s="372"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -15528,59 +15608,59 @@
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="369" t="s">
+      <c r="B3" s="371" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="369"/>
-      <c r="D3" s="370" t="s">
+      <c r="C3" s="371"/>
+      <c r="D3" s="372" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="370"/>
-      <c r="F3" s="348" t="s">
+      <c r="E3" s="372"/>
+      <c r="F3" s="350" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="348" t="s">
+      <c r="G3" s="350" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="348" t="s">
+      <c r="H3" s="350" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="348" t="s">
+      <c r="I3" s="350" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="348" t="s">
+      <c r="J3" s="350" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="348" t="s">
+      <c r="K3" s="350" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="348" t="s">
+      <c r="L3" s="350" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="348" t="s">
+      <c r="M3" s="350" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="355" t="s">
+      <c r="N3" s="357" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="355" t="s">
+      <c r="O3" s="357" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="354"/>
-      <c r="Q3" s="356" t="s">
+      <c r="P3" s="356"/>
+      <c r="Q3" s="358" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="357"/>
-      <c r="S3" s="358"/>
-      <c r="T3" s="359" t="s">
+      <c r="R3" s="359"/>
+      <c r="S3" s="360"/>
+      <c r="T3" s="361" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="360"/>
-      <c r="V3" s="361"/>
-      <c r="W3" s="352" t="s">
+      <c r="U3" s="362"/>
+      <c r="V3" s="363"/>
+      <c r="W3" s="354" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="352" t="s">
+      <c r="X3" s="354" t="s">
         <v>162</v>
       </c>
     </row>
@@ -15598,17 +15678,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="348"/>
-      <c r="G4" s="349"/>
-      <c r="H4" s="349"/>
-      <c r="I4" s="348"/>
-      <c r="J4" s="348"/>
-      <c r="K4" s="348"/>
-      <c r="L4" s="348"/>
-      <c r="M4" s="348"/>
-      <c r="N4" s="355"/>
-      <c r="O4" s="355"/>
-      <c r="P4" s="354"/>
+      <c r="F4" s="350"/>
+      <c r="G4" s="351"/>
+      <c r="H4" s="351"/>
+      <c r="I4" s="350"/>
+      <c r="J4" s="350"/>
+      <c r="K4" s="350"/>
+      <c r="L4" s="350"/>
+      <c r="M4" s="350"/>
+      <c r="N4" s="357"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="356"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -15627,8 +15707,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="353"/>
-      <c r="X4" s="353"/>
+      <c r="W4" s="355"/>
+      <c r="X4" s="355"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -16644,7 +16724,7 @@
       </c>
     </row>
     <row r="20" spans="1:24" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="347" t="s">
+      <c r="A20" s="349" t="s">
         <v>185</v>
       </c>
       <c r="B20" s="295">
@@ -16713,7 +16793,7 @@
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="347"/>
+      <c r="A21" s="349"/>
       <c r="B21" s="295">
         <v>33</v>
       </c>
@@ -16780,7 +16860,7 @@
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="347"/>
+      <c r="A22" s="349"/>
       <c r="B22" s="295">
         <v>29</v>
       </c>
@@ -16845,7 +16925,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="347"/>
+      <c r="A23" s="349"/>
       <c r="B23" s="295">
         <v>0</v>
       </c>
@@ -16910,7 +16990,7 @@
       </c>
     </row>
     <row r="24" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="347"/>
+      <c r="A24" s="349"/>
       <c r="B24" s="295">
         <v>4</v>
       </c>
@@ -20945,7 +21025,7 @@
       <c r="AA82" s="255"/>
     </row>
     <row r="83" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="347" t="s">
+      <c r="A83" s="349" t="s">
         <v>186</v>
       </c>
       <c r="B83" s="295">
@@ -21017,7 +21097,7 @@
       <c r="AA83" s="255"/>
     </row>
     <row r="84" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="347"/>
+      <c r="A84" s="349"/>
       <c r="B84" s="295">
         <v>33</v>
       </c>
@@ -21089,7 +21169,7 @@
       <c r="AA84" s="255"/>
     </row>
     <row r="85" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="347"/>
+      <c r="A85" s="349"/>
       <c r="B85" s="295">
         <v>29</v>
       </c>
@@ -21157,7 +21237,7 @@
       <c r="AA85" s="255"/>
     </row>
     <row r="86" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="347"/>
+      <c r="A86" s="349"/>
       <c r="B86" s="295">
         <v>0</v>
       </c>
@@ -29352,20 +29432,20 @@
       <c r="C208" s="295">
         <v>41</v>
       </c>
-      <c r="D208" s="147">
+      <c r="D208" s="126">
         <f>'Data Ocupacion'!BJ31</f>
-        <v>0</v>
-      </c>
-      <c r="E208" s="147">
+        <v>38</v>
+      </c>
+      <c r="E208" s="126">
         <f>'Data Ocupacion'!BK31</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F208" s="220" t="s">
         <v>38</v>
       </c>
       <c r="G208" s="221">
         <f t="shared" ref="G208:G213" si="174">D208+E208*2</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H208" s="125">
         <f>B208+C208*2</f>
@@ -29373,28 +29453,30 @@
       </c>
       <c r="I208" s="222">
         <f t="shared" ref="I208:I213" si="175">D208+E208</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J208" s="222">
         <f>G208*M$2</f>
-        <v>0</v>
+        <v>5175.6000000000004</v>
       </c>
       <c r="K208" s="153">
         <f>I208*M$2</f>
-        <v>0</v>
+        <v>3407.27</v>
       </c>
       <c r="L208" s="125">
         <f t="shared" ref="L208:L213" si="176">J208*104</f>
-        <v>0</v>
+        <v>538262.4</v>
       </c>
       <c r="M208" s="125">
         <f t="shared" ref="M208:M213" si="177">I208*104</f>
-        <v>0</v>
+        <v>8216</v>
       </c>
       <c r="N208" s="19"/>
       <c r="O208" s="19"/>
       <c r="P208" s="146"/>
-      <c r="Q208" s="244"/>
+      <c r="Q208" s="244">
+        <v>3</v>
+      </c>
       <c r="R208" s="183"/>
       <c r="S208" s="206"/>
       <c r="T208" s="244"/>
@@ -29402,7 +29484,7 @@
       <c r="V208" s="228"/>
       <c r="W208" s="182">
         <f>J208-(Q208*($M$2-$K$1))-(R208*($M$2-$M$1))- (S208*($M$2-$I$2))+ (T208*($G$2))</f>
-        <v>0</v>
+        <v>5122.4100000000008</v>
       </c>
       <c r="X208" s="182">
         <f>H208*$M$2</f>
@@ -29419,18 +29501,18 @@
       </c>
       <c r="D209" s="126">
         <f>'Data Ocupacion'!BJ32</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E209" s="126">
         <f>'Data Ocupacion'!BK32</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F209" s="220" t="s">
         <v>52</v>
       </c>
       <c r="G209" s="221">
         <f t="shared" si="174"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H209" s="125">
         <f t="shared" ref="H209:H213" si="178">B209+C209*2</f>
@@ -29438,23 +29520,23 @@
       </c>
       <c r="I209" s="125">
         <f t="shared" si="175"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J209" s="125">
         <f>G209*M$2</f>
-        <v>0</v>
+        <v>5175.6000000000004</v>
       </c>
       <c r="K209" s="153">
         <f>I209*M$2</f>
-        <v>0</v>
+        <v>3364.1400000000003</v>
       </c>
       <c r="L209" s="125">
         <f t="shared" si="176"/>
-        <v>0</v>
+        <v>538262.4</v>
       </c>
       <c r="M209" s="125">
         <f t="shared" si="177"/>
-        <v>0</v>
+        <v>8112</v>
       </c>
       <c r="N209" s="19"/>
       <c r="O209" s="19"/>
@@ -29467,7 +29549,7 @@
       <c r="V209" s="206"/>
       <c r="W209" s="185">
         <f>J209-(T209*($M$2-$K$1)+(U209*($M$2-$M$1)))</f>
-        <v>0</v>
+        <v>5175.6000000000004</v>
       </c>
       <c r="X209" s="182">
         <f>H209*$M$2</f>
@@ -29484,18 +29566,18 @@
       </c>
       <c r="D210" s="147">
         <f>'Data Ocupacion'!BJ33</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E210" s="147">
         <f>'Data Ocupacion'!BK33</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F210" s="220" t="s">
         <v>36</v>
       </c>
       <c r="G210" s="221">
         <f t="shared" si="174"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H210" s="125">
         <f t="shared" si="178"/>
@@ -29503,28 +29585,30 @@
       </c>
       <c r="I210" s="125">
         <f t="shared" si="175"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J210" s="125">
         <f>G210*M$1</f>
-        <v>0</v>
+        <v>1106.18</v>
       </c>
       <c r="K210" s="153">
         <f>I210*M$1</f>
-        <v>0</v>
+        <v>1047.96</v>
       </c>
       <c r="L210" s="125">
         <f t="shared" si="176"/>
-        <v>0</v>
+        <v>115042.72</v>
       </c>
       <c r="M210" s="125">
         <f t="shared" si="177"/>
-        <v>0</v>
+        <v>3744</v>
       </c>
       <c r="N210" s="19"/>
       <c r="O210" s="19"/>
       <c r="P210" s="146"/>
-      <c r="Q210" s="244"/>
+      <c r="Q210" s="244">
+        <v>2</v>
+      </c>
       <c r="R210" s="187"/>
       <c r="S210" s="207"/>
       <c r="T210" s="188"/>
@@ -29532,7 +29616,7 @@
       <c r="V210" s="189"/>
       <c r="W210" s="182">
         <f>J210-(Q210*($M$1-$K$1))</f>
-        <v>0</v>
+        <v>1098.76</v>
       </c>
       <c r="X210" s="182">
         <f>H210*$M$1</f>
@@ -29549,18 +29633,18 @@
       </c>
       <c r="D211" s="147">
         <f>'Data Ocupacion'!BJ34</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E211" s="147">
         <f>'Data Ocupacion'!BK34</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F211" s="220" t="s">
         <v>53</v>
       </c>
       <c r="G211" s="221">
         <f t="shared" si="174"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H211" s="125">
         <f t="shared" si="178"/>
@@ -29568,23 +29652,23 @@
       </c>
       <c r="I211" s="125">
         <f t="shared" si="175"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J211" s="125">
         <f>G211*M$1</f>
-        <v>0</v>
+        <v>989.74</v>
       </c>
       <c r="K211" s="153">
         <f>I211*M$1</f>
-        <v>0</v>
+        <v>931.52</v>
       </c>
       <c r="L211" s="125">
         <f t="shared" si="176"/>
-        <v>0</v>
+        <v>102932.96</v>
       </c>
       <c r="M211" s="125">
         <f t="shared" si="177"/>
-        <v>0</v>
+        <v>3328</v>
       </c>
       <c r="N211" s="19"/>
       <c r="O211" s="19"/>
@@ -29597,7 +29681,7 @@
       <c r="V211" s="189"/>
       <c r="W211" s="182">
         <f>J211</f>
-        <v>0</v>
+        <v>989.74</v>
       </c>
       <c r="X211" s="182">
         <f>H211*$M$1</f>
@@ -29677,11 +29761,11 @@
       <c r="C213" s="295">
         <v>0</v>
       </c>
-      <c r="D213" s="147">
+      <c r="D213" s="126">
         <f>'Data Ocupacion'!BJ36</f>
-        <v>0</v>
-      </c>
-      <c r="E213" s="147">
+        <v>4</v>
+      </c>
+      <c r="E213" s="126">
         <f>'Data Ocupacion'!BK36</f>
         <v>0</v>
       </c>
@@ -29690,7 +29774,7 @@
       </c>
       <c r="G213" s="221">
         <f t="shared" si="174"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H213" s="125">
         <f t="shared" si="178"/>
@@ -29698,23 +29782,23 @@
       </c>
       <c r="I213" s="224">
         <f t="shared" si="175"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J213" s="224">
         <f>G213*K$1</f>
-        <v>0</v>
+        <v>101.6</v>
       </c>
       <c r="K213" s="153">
         <f>I213*K$1</f>
-        <v>0</v>
+        <v>101.6</v>
       </c>
       <c r="L213" s="125">
         <f t="shared" si="176"/>
-        <v>0</v>
+        <v>10566.4</v>
       </c>
       <c r="M213" s="125">
         <f t="shared" si="177"/>
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="N213" s="19"/>
       <c r="O213" s="19"/>
@@ -29727,7 +29811,7 @@
       <c r="V213" s="189"/>
       <c r="W213" s="182">
         <f>J213</f>
-        <v>0</v>
+        <v>101.6</v>
       </c>
       <c r="X213" s="182">
         <f>H213*$K$1</f>
@@ -29746,16 +29830,16 @@
       </c>
       <c r="D214" s="148">
         <f>SUM(D208:D213)</f>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="E214" s="148">
         <f>SUM(E208:E213)</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F214" s="119"/>
       <c r="G214" s="119">
         <f t="shared" ref="G214:M214" si="179">SUM(G208:G213)</f>
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="H214" s="119">
         <f t="shared" si="179"/>
@@ -29763,31 +29847,31 @@
       </c>
       <c r="I214" s="119">
         <f t="shared" si="179"/>
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="J214" s="119">
         <f t="shared" si="179"/>
-        <v>0</v>
+        <v>12548.720000000001</v>
       </c>
       <c r="K214" s="119">
         <f t="shared" si="179"/>
-        <v>0</v>
+        <v>8852.49</v>
       </c>
       <c r="L214" s="119">
         <f t="shared" si="179"/>
-        <v>0</v>
+        <v>1305066.8799999999</v>
       </c>
       <c r="M214" s="119">
         <f t="shared" si="179"/>
-        <v>0</v>
+        <v>23816</v>
       </c>
       <c r="N214" s="123">
         <f>'Odometro-Kilometraje'!AE88</f>
-        <v>-63937011</v>
+        <v>12797</v>
       </c>
       <c r="O214" s="21">
         <f>(W214/N214)*100</f>
-        <v>0</v>
+        <v>97.586231147925318</v>
       </c>
       <c r="P214" s="192"/>
       <c r="Q214" s="181"/>
@@ -29798,7 +29882,7 @@
       <c r="V214" s="181"/>
       <c r="W214" s="193">
         <f>SUM(W208:W213)</f>
-        <v>0</v>
+        <v>12488.110000000002</v>
       </c>
       <c r="X214" s="193">
         <f>SUM(X208:X213)</f>
@@ -30281,38 +30365,38 @@
     <row r="222" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="223" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223"/>
-      <c r="B223" s="364" t="s">
+      <c r="B223" s="366" t="s">
         <v>56</v>
       </c>
-      <c r="C223" s="365"/>
-      <c r="D223" s="365"/>
-      <c r="E223" s="365"/>
-      <c r="F223" s="365"/>
-      <c r="G223" s="366"/>
+      <c r="C223" s="367"/>
+      <c r="D223" s="367"/>
+      <c r="E223" s="367"/>
+      <c r="F223" s="367"/>
+      <c r="G223" s="368"/>
       <c r="H223" s="290"/>
-      <c r="I223" s="364" t="s">
+      <c r="I223" s="366" t="s">
         <v>57</v>
       </c>
-      <c r="J223" s="365"/>
-      <c r="K223" s="365"/>
-      <c r="L223" s="365"/>
-      <c r="M223" s="365"/>
-      <c r="N223" s="366"/>
-      <c r="P223" s="362" t="s">
+      <c r="J223" s="367"/>
+      <c r="K223" s="367"/>
+      <c r="L223" s="367"/>
+      <c r="M223" s="367"/>
+      <c r="N223" s="368"/>
+      <c r="P223" s="364" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="362"/>
-      <c r="R223" s="362"/>
-      <c r="S223" s="363"/>
-      <c r="T223" s="359" t="s">
+      <c r="Q223" s="364"/>
+      <c r="R223" s="364"/>
+      <c r="S223" s="365"/>
+      <c r="T223" s="361" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="360"/>
-      <c r="V223" s="361"/>
-      <c r="W223" s="350" t="s">
+      <c r="U223" s="362"/>
+      <c r="V223" s="363"/>
+      <c r="W223" s="352" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="350" t="s">
+      <c r="X223" s="352" t="s">
         <v>162</v>
       </c>
     </row>
@@ -30378,8 +30462,8 @@
       <c r="V224" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="351"/>
-      <c r="X224" s="351"/>
+      <c r="W224" s="353"/>
+      <c r="X224" s="353"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -30412,32 +30496,32 @@
       <c r="H225" s="139"/>
       <c r="I225" s="114">
         <f t="shared" ref="I225:J230" si="189">D5+D12+D26+D33+D40+D47+D54+D61+D68+D75+D82+D89+D96+D103+D110+D117+D124+D131+D138+D145+D152+D159+D166+D173+D180+D187+D194+D201+D208+D19</f>
-        <v>1308</v>
+        <v>1346</v>
       </c>
       <c r="J225" s="114">
         <f t="shared" si="189"/>
-        <v>830</v>
+        <v>871</v>
       </c>
       <c r="K225" s="114">
         <f t="shared" ref="K225:K230" si="190">I225+J225</f>
-        <v>2138</v>
+        <v>2217</v>
       </c>
       <c r="L225" s="139">
         <f>K225*43.13</f>
-        <v>92211.94</v>
+        <v>95619.21</v>
       </c>
       <c r="M225" s="139">
         <f>I225*43.13+J225*86.26</f>
-        <v>128009.84</v>
+        <v>133185.44</v>
       </c>
       <c r="N225" s="139">
         <f t="shared" ref="N225:N230" si="191">M225*104</f>
-        <v>13313023.359999999</v>
+        <v>13851285.76</v>
       </c>
       <c r="O225" s="124"/>
       <c r="P225" s="209">
         <f>SUM(Q194,Q187,Q180,Q173,Q166,Q159,Q152,Q145,Q138,Q131,Q124,Q117,Q110,Q103,Q96,Q89,Q82,Q75,Q68,Q61,Q54,Q47,Q40,Q33,Q26,Q19,Q12,Q5,Q201,Q208,Q215)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Q225" s="209">
         <f>SUM(R194,R187,R180,R173,R166,R159,R152,R145,R138,R131,R124,R117,R110,R103,R96,R89,R82,R75,R68,R61,R54,R47,R40,R33,R26,R19,R12,R5,R201,R208,R215)</f>
@@ -30465,7 +30549,7 @@
       </c>
       <c r="W225" s="231">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214</f>
-        <v>298757.06000000006</v>
+        <v>311245.17000000004</v>
       </c>
       <c r="X225" s="231">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214</f>
@@ -30503,27 +30587,27 @@
       <c r="H226" s="139"/>
       <c r="I226" s="114">
         <f t="shared" si="189"/>
-        <v>1323</v>
+        <v>1359</v>
       </c>
       <c r="J226" s="114">
         <f t="shared" si="189"/>
-        <v>822</v>
+        <v>864</v>
       </c>
       <c r="K226" s="114">
         <f t="shared" si="190"/>
-        <v>2145</v>
+        <v>2223</v>
       </c>
       <c r="L226" s="139">
         <f t="shared" ref="L226" si="192">K226*43.13</f>
-        <v>92513.85</v>
+        <v>95877.99</v>
       </c>
       <c r="M226" s="139">
         <f>I226*43.13+J226*86.26</f>
-        <v>127966.71</v>
+        <v>133142.31</v>
       </c>
       <c r="N226" s="139">
         <f t="shared" si="191"/>
-        <v>13308537.84</v>
+        <v>13846800.24</v>
       </c>
       <c r="O226" s="124"/>
       <c r="W226" s="124"/>
@@ -30560,27 +30644,27 @@
       <c r="H227" s="139"/>
       <c r="I227" s="114">
         <f t="shared" si="189"/>
-        <v>661</v>
+        <v>695</v>
       </c>
       <c r="J227" s="114">
         <f t="shared" si="189"/>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K227" s="114">
         <f t="shared" si="190"/>
-        <v>718</v>
+        <v>754</v>
       </c>
       <c r="L227" s="139">
         <f>K227*29.11</f>
-        <v>20900.98</v>
+        <v>21948.94</v>
       </c>
       <c r="M227" s="139">
         <f>I227*29.11+J227*58.22</f>
-        <v>22560.25</v>
+        <v>23666.43</v>
       </c>
       <c r="N227" s="139">
         <f t="shared" si="191"/>
-        <v>2346266</v>
+        <v>2461308.7200000002</v>
       </c>
       <c r="O227" s="124"/>
       <c r="W227" s="124"/>
@@ -30616,27 +30700,27 @@
       <c r="H228" s="139"/>
       <c r="I228" s="114">
         <f t="shared" si="189"/>
-        <v>583</v>
+        <v>613</v>
       </c>
       <c r="J228" s="114">
         <f t="shared" si="189"/>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K228" s="114">
         <f t="shared" si="190"/>
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="L228" s="139">
         <f>K228*29.11</f>
-        <v>18630.400000000001</v>
+        <v>19561.919999999998</v>
       </c>
       <c r="M228" s="139">
         <f>I228*29.11+J228*58.22</f>
-        <v>20289.670000000002</v>
+        <v>21279.41</v>
       </c>
       <c r="N228" s="139">
         <f t="shared" si="191"/>
-        <v>2110125.6800000002</v>
+        <v>2213058.64</v>
       </c>
       <c r="O228" s="124"/>
       <c r="W228" s="124"/>
@@ -30731,7 +30815,7 @@
       <c r="H230" s="139"/>
       <c r="I230" s="114">
         <f t="shared" si="189"/>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J230" s="114">
         <f t="shared" si="189"/>
@@ -30739,19 +30823,19 @@
       </c>
       <c r="K230" s="114">
         <f t="shared" si="190"/>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L230" s="139">
         <f>K230*25.4</f>
-        <v>2006.6</v>
+        <v>2108.1999999999998</v>
       </c>
       <c r="M230" s="139">
         <f>I230*25.4+J230*50.8</f>
-        <v>2006.6</v>
+        <v>2108.1999999999998</v>
       </c>
       <c r="N230" s="139">
         <f t="shared" si="191"/>
-        <v>208686.4</v>
+        <v>219252.8</v>
       </c>
       <c r="O230" s="124"/>
       <c r="P230" s="124"/>
@@ -30816,27 +30900,27 @@
       <c r="H232" s="284"/>
       <c r="I232" s="284">
         <f>SUM(I225:I230)</f>
-        <v>3954</v>
+        <v>4096</v>
       </c>
       <c r="J232" s="284">
         <f>SUM(J225:J230)</f>
-        <v>1766</v>
+        <v>1853</v>
       </c>
       <c r="K232" s="284">
         <f>SUM(K225:K231)</f>
-        <v>5720</v>
+        <v>5949</v>
       </c>
       <c r="L232" s="284">
         <f>SUM(L225:L231)</f>
-        <v>226263.77000000002</v>
+        <v>235116.26</v>
       </c>
       <c r="M232" s="284">
         <f>SUM(M225:M231)</f>
-        <v>300833.06999999995</v>
+        <v>313381.78999999998</v>
       </c>
       <c r="N232" s="284">
         <f>SUM(N225:N231)</f>
-        <v>31286639.279999997</v>
+        <v>32591706.16</v>
       </c>
       <c r="P232"/>
       <c r="Q232"/>
@@ -30876,7 +30960,7 @@
       </c>
       <c r="G234" s="124">
         <f>(I232)+(J232*2)</f>
-        <v>7486</v>
+        <v>7802</v>
       </c>
       <c r="I234" s="124"/>
       <c r="J234" s="198"/>
@@ -30889,10 +30973,10 @@
     </row>
     <row r="235" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A235" s="24"/>
-      <c r="B235" s="367" t="s">
+      <c r="B235" s="369" t="s">
         <v>55</v>
       </c>
-      <c r="C235" s="368"/>
+      <c r="C235" s="370"/>
       <c r="D235" s="25" t="s">
         <v>65</v>
       </c>
@@ -31028,7 +31112,7 @@
       </c>
       <c r="J239" s="219">
         <f>(I232)+(J232*2)</f>
-        <v>7486</v>
+        <v>7802</v>
       </c>
       <c r="K239" s="124"/>
       <c r="L239" s="124"/>
@@ -31354,126 +31438,126 @@
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
-      <c r="D1" s="371">
+      <c r="D1" s="373">
         <v>46174</v>
       </c>
-      <c r="E1" s="371"/>
-      <c r="F1" s="371">
+      <c r="E1" s="373"/>
+      <c r="F1" s="373">
         <v>46175</v>
       </c>
-      <c r="G1" s="371"/>
-      <c r="H1" s="371">
+      <c r="G1" s="373"/>
+      <c r="H1" s="373">
         <v>46176</v>
       </c>
-      <c r="I1" s="371"/>
-      <c r="J1" s="371">
+      <c r="I1" s="373"/>
+      <c r="J1" s="373">
         <v>46146</v>
       </c>
-      <c r="K1" s="371"/>
-      <c r="L1" s="371">
+      <c r="K1" s="373"/>
+      <c r="L1" s="373">
         <v>46147</v>
       </c>
-      <c r="M1" s="371"/>
-      <c r="N1" s="371">
+      <c r="M1" s="373"/>
+      <c r="N1" s="373">
         <v>46148</v>
       </c>
-      <c r="O1" s="371"/>
-      <c r="P1" s="371">
+      <c r="O1" s="373"/>
+      <c r="P1" s="373">
         <v>46149</v>
       </c>
-      <c r="Q1" s="371"/>
-      <c r="R1" s="371">
+      <c r="Q1" s="373"/>
+      <c r="R1" s="373">
         <v>46150</v>
       </c>
-      <c r="S1" s="371"/>
-      <c r="T1" s="371">
+      <c r="S1" s="373"/>
+      <c r="T1" s="373">
         <v>46151</v>
       </c>
-      <c r="U1" s="371"/>
-      <c r="V1" s="371">
+      <c r="U1" s="373"/>
+      <c r="V1" s="373">
         <v>46152</v>
       </c>
-      <c r="W1" s="371"/>
-      <c r="X1" s="371">
+      <c r="W1" s="373"/>
+      <c r="X1" s="373">
         <v>46153</v>
       </c>
-      <c r="Y1" s="371"/>
-      <c r="Z1" s="371">
+      <c r="Y1" s="373"/>
+      <c r="Z1" s="373">
         <v>46154</v>
       </c>
-      <c r="AA1" s="371"/>
-      <c r="AB1" s="371">
+      <c r="AA1" s="373"/>
+      <c r="AB1" s="373">
         <v>46155</v>
       </c>
-      <c r="AC1" s="371"/>
-      <c r="AD1" s="371">
+      <c r="AC1" s="373"/>
+      <c r="AD1" s="373">
         <v>46156</v>
       </c>
-      <c r="AE1" s="371"/>
-      <c r="AF1" s="371">
+      <c r="AE1" s="373"/>
+      <c r="AF1" s="373">
         <v>46157</v>
       </c>
-      <c r="AG1" s="371"/>
-      <c r="AH1" s="371">
+      <c r="AG1" s="373"/>
+      <c r="AH1" s="373">
         <v>46158</v>
       </c>
-      <c r="AI1" s="371"/>
-      <c r="AJ1" s="371">
+      <c r="AI1" s="373"/>
+      <c r="AJ1" s="373">
         <v>46159</v>
       </c>
-      <c r="AK1" s="371"/>
-      <c r="AL1" s="371">
+      <c r="AK1" s="373"/>
+      <c r="AL1" s="373">
         <v>46160</v>
       </c>
-      <c r="AM1" s="371"/>
-      <c r="AN1" s="371">
+      <c r="AM1" s="373"/>
+      <c r="AN1" s="373">
         <v>46161</v>
       </c>
-      <c r="AO1" s="371"/>
-      <c r="AP1" s="371">
+      <c r="AO1" s="373"/>
+      <c r="AP1" s="373">
         <v>46162</v>
       </c>
-      <c r="AQ1" s="371"/>
-      <c r="AR1" s="371">
+      <c r="AQ1" s="373"/>
+      <c r="AR1" s="373">
         <v>46163</v>
       </c>
-      <c r="AS1" s="371"/>
-      <c r="AT1" s="371">
+      <c r="AS1" s="373"/>
+      <c r="AT1" s="373">
         <v>46164</v>
       </c>
-      <c r="AU1" s="371"/>
-      <c r="AV1" s="371">
+      <c r="AU1" s="373"/>
+      <c r="AV1" s="373">
         <v>46165</v>
       </c>
-      <c r="AW1" s="371"/>
-      <c r="AX1" s="371">
+      <c r="AW1" s="373"/>
+      <c r="AX1" s="373">
         <v>46166</v>
       </c>
-      <c r="AY1" s="371"/>
-      <c r="AZ1" s="371">
+      <c r="AY1" s="373"/>
+      <c r="AZ1" s="373">
         <v>46167</v>
       </c>
-      <c r="BA1" s="371"/>
-      <c r="BB1" s="371">
+      <c r="BA1" s="373"/>
+      <c r="BB1" s="373">
         <v>46168</v>
       </c>
-      <c r="BC1" s="371"/>
-      <c r="BD1" s="371">
+      <c r="BC1" s="373"/>
+      <c r="BD1" s="373">
         <v>46169</v>
       </c>
-      <c r="BE1" s="371"/>
-      <c r="BF1" s="371">
+      <c r="BE1" s="373"/>
+      <c r="BF1" s="373">
         <v>46170</v>
       </c>
-      <c r="BG1" s="371"/>
-      <c r="BH1" s="371">
+      <c r="BG1" s="373"/>
+      <c r="BH1" s="373">
         <v>46171</v>
       </c>
-      <c r="BI1" s="371"/>
-      <c r="BJ1" s="371">
+      <c r="BI1" s="373"/>
+      <c r="BJ1" s="373">
         <v>46172</v>
       </c>
-      <c r="BK1" s="371"/>
+      <c r="BK1" s="373"/>
     </row>
     <row r="2" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
@@ -31838,8 +31922,12 @@
       <c r="BI3" s="309">
         <v>0</v>
       </c>
-      <c r="BJ3" s="156"/>
-      <c r="BK3" s="156"/>
+      <c r="BJ3" s="156">
+        <v>10</v>
+      </c>
+      <c r="BK3" s="156">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
@@ -32021,8 +32109,12 @@
       <c r="BI4" s="309">
         <v>0</v>
       </c>
-      <c r="BJ4" s="156"/>
-      <c r="BK4" s="156"/>
+      <c r="BJ4" s="156">
+        <v>0</v>
+      </c>
+      <c r="BK4" s="156">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A5" s="67" t="s">
@@ -32204,8 +32296,12 @@
       <c r="BI5" s="309">
         <v>1</v>
       </c>
-      <c r="BJ5" s="156"/>
-      <c r="BK5" s="156"/>
+      <c r="BJ5" s="156">
+        <v>2</v>
+      </c>
+      <c r="BK5" s="156">
+        <v>8</v>
+      </c>
     </row>
     <row r="6" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A6" s="67" t="s">
@@ -32387,8 +32483,12 @@
       <c r="BI6" s="309">
         <v>0</v>
       </c>
-      <c r="BJ6" s="156"/>
-      <c r="BK6" s="156"/>
+      <c r="BJ6" s="156">
+        <v>10</v>
+      </c>
+      <c r="BK6" s="156">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A7" s="67" t="s">
@@ -32570,8 +32670,12 @@
       <c r="BI7" s="309">
         <v>0</v>
       </c>
-      <c r="BJ7" s="156"/>
-      <c r="BK7" s="156"/>
+      <c r="BJ7" s="156">
+        <v>1</v>
+      </c>
+      <c r="BK7" s="156">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="67" t="s">
@@ -32753,8 +32857,12 @@
       <c r="BI8" s="309">
         <v>0</v>
       </c>
-      <c r="BJ8" s="156"/>
-      <c r="BK8" s="156"/>
+      <c r="BJ8" s="156">
+        <v>4</v>
+      </c>
+      <c r="BK8" s="156">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A9" s="53"/>
@@ -33045,8 +33153,12 @@
       <c r="BI10" s="309">
         <v>0</v>
       </c>
-      <c r="BJ10" s="156"/>
-      <c r="BK10" s="156"/>
+      <c r="BJ10" s="156">
+        <v>17</v>
+      </c>
+      <c r="BK10" s="156">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="70" t="s">
@@ -33228,8 +33340,12 @@
       <c r="BI11" s="309">
         <v>0</v>
       </c>
-      <c r="BJ11" s="156"/>
-      <c r="BK11" s="156"/>
+      <c r="BJ11" s="156">
+        <v>0</v>
+      </c>
+      <c r="BK11" s="156">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A12" s="72" t="s">
@@ -33411,8 +33527,12 @@
       <c r="BI12" s="309">
         <v>2</v>
       </c>
-      <c r="BJ12" s="156"/>
-      <c r="BK12" s="156"/>
+      <c r="BJ12" s="156">
+        <v>35</v>
+      </c>
+      <c r="BK12" s="156">
+        <v>26</v>
+      </c>
     </row>
     <row r="13" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A13" s="72" t="s">
@@ -33594,8 +33714,12 @@
       <c r="BI13" s="309">
         <v>0</v>
       </c>
-      <c r="BJ13" s="156"/>
-      <c r="BK13" s="156"/>
+      <c r="BJ13" s="156">
+        <v>14</v>
+      </c>
+      <c r="BK13" s="156">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="74" t="s">
@@ -33777,8 +33901,12 @@
       <c r="BI14" s="309">
         <v>0</v>
       </c>
-      <c r="BJ14" s="156"/>
-      <c r="BK14" s="156"/>
+      <c r="BJ14" s="156">
+        <v>3</v>
+      </c>
+      <c r="BK14" s="156">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A15" s="261" t="s">
@@ -33960,8 +34088,12 @@
       <c r="BI15" s="309">
         <v>0</v>
       </c>
-      <c r="BJ15" s="156"/>
-      <c r="BK15" s="156"/>
+      <c r="BJ15" s="156">
+        <v>28</v>
+      </c>
+      <c r="BK15" s="156">
+        <v>33</v>
+      </c>
     </row>
     <row r="16" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="306"/>
@@ -34252,8 +34384,12 @@
       <c r="BI17" s="309">
         <v>0</v>
       </c>
-      <c r="BJ17" s="286"/>
-      <c r="BK17" s="286"/>
+      <c r="BJ17" s="286">
+        <v>7</v>
+      </c>
+      <c r="BK17" s="286">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:63 16295:16295" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67" t="s">
@@ -34435,8 +34571,12 @@
       <c r="BI18" s="309">
         <v>0</v>
       </c>
-      <c r="BJ18" s="286"/>
-      <c r="BK18" s="286"/>
+      <c r="BJ18" s="286">
+        <v>0</v>
+      </c>
+      <c r="BK18" s="286">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:63 16295:16295" x14ac:dyDescent="0.25">
       <c r="A19" s="67" t="s">
@@ -34618,8 +34758,12 @@
       <c r="BI19" s="309">
         <v>0</v>
       </c>
-      <c r="BJ19" s="286"/>
-      <c r="BK19" s="286"/>
+      <c r="BJ19" s="286">
+        <v>1</v>
+      </c>
+      <c r="BK19" s="286">
+        <v>7</v>
+      </c>
     </row>
     <row r="20" spans="1:63 16295:16295" x14ac:dyDescent="0.25">
       <c r="A20" s="67" t="s">
@@ -34801,8 +34945,12 @@
       <c r="BI20" s="309">
         <v>0</v>
       </c>
-      <c r="BJ20" s="286"/>
-      <c r="BK20" s="286"/>
+      <c r="BJ20" s="286">
+        <v>6</v>
+      </c>
+      <c r="BK20" s="286">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:63 16295:16295" x14ac:dyDescent="0.25">
       <c r="A21" s="67" t="s">
@@ -34984,8 +35132,12 @@
       <c r="BI21" s="309">
         <v>0</v>
       </c>
-      <c r="BJ21" s="286"/>
-      <c r="BK21" s="286"/>
+      <c r="BJ21" s="286">
+        <v>0</v>
+      </c>
+      <c r="BK21" s="286">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:63 16295:16295" x14ac:dyDescent="0.25">
       <c r="A22" s="67" t="s">
@@ -35167,8 +35319,12 @@
       <c r="BI22" s="309">
         <v>0</v>
       </c>
-      <c r="BJ22" s="286"/>
-      <c r="BK22" s="286"/>
+      <c r="BJ22" s="286">
+        <v>4</v>
+      </c>
+      <c r="BK22" s="286">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:63 16295:16295" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="8"/>
@@ -35469,11 +35625,11 @@
       </c>
       <c r="BJ24" s="137">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="BK24" s="137">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="XBS24" s="64"/>
     </row>
@@ -35921,11 +36077,11 @@
       </c>
       <c r="BJ31" s="324">
         <f>BJ5+BJ12+BJ19</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BK31" s="324">
         <f>BK5+BK12+BK19</f>
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:63 16295:16295" x14ac:dyDescent="0.25">
@@ -36167,11 +36323,11 @@
       </c>
       <c r="BJ32" s="324">
         <f>BJ8+BJ15+BJ22</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BK32" s="324">
         <f>BK8+BK15+BK22</f>
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:63" x14ac:dyDescent="0.25">
@@ -36413,11 +36569,11 @@
       </c>
       <c r="BJ33" s="324">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BK33" s="324">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:63" x14ac:dyDescent="0.25">
@@ -36659,11 +36815,11 @@
       </c>
       <c r="BJ34" s="324">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BK34" s="324">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -37151,7 +37307,7 @@
       </c>
       <c r="BJ36" s="324">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK36" s="324">
         <f t="shared" si="13"/>
@@ -37159,10 +37315,10 @@
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A37" s="372" t="s">
+      <c r="A37" s="374" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="372"/>
+      <c r="B37" s="374"/>
       <c r="C37" s="8"/>
       <c r="D37" s="149">
         <f t="shared" ref="D37:AI37" si="14">SUM(D31:D36)</f>
@@ -37398,11 +37554,11 @@
       </c>
       <c r="BJ37" s="324">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="BK37" s="324">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:63" x14ac:dyDescent="0.25">
@@ -37643,7 +37799,7 @@
       <c r="BI40" s="324"/>
       <c r="BJ40" s="324">
         <f>BJ5+BK5+BJ12+BK12+BJ19+BK19</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="BK40" s="324"/>
     </row>
@@ -37799,7 +37955,7 @@
       <c r="BI41" s="324"/>
       <c r="BJ41" s="324">
         <f>BJ8+BK8+BJ15+BK15+BJ22+BK22</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="BK41" s="324"/>
     </row>
@@ -37955,7 +38111,7 @@
       <c r="BI42" s="324"/>
       <c r="BJ42" s="324">
         <f>BJ3+BK3+BJ10+BK10+BJ17+BK17</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BK42" s="324"/>
     </row>
@@ -38111,7 +38267,7 @@
       <c r="BI43" s="324"/>
       <c r="BJ43" s="324">
         <f>BJ6+BK6+BJ13+BK13+BJ20+BK20</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BK43" s="324"/>
     </row>
@@ -38423,7 +38579,7 @@
       <c r="BI45" s="324"/>
       <c r="BJ45" s="324">
         <f>BJ7+BK7+BJ14+BK14+BJ21+BK21</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK45" s="324"/>
     </row>
@@ -38709,7 +38865,7 @@
       <c r="BI48" s="324"/>
       <c r="BJ48" s="324">
         <f>(BJ5+BJ12+BJ19)+2*(BK5+BK12+BK19)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BK48" s="324"/>
     </row>
@@ -38865,7 +39021,7 @@
       <c r="BI49" s="324"/>
       <c r="BJ49" s="324">
         <f>(BJ8+BJ15+BJ22)+2*(BK8+BK15+BK22)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BK49" s="324"/>
     </row>
@@ -39021,7 +39177,7 @@
       <c r="BI50" s="324"/>
       <c r="BJ50" s="324">
         <f>(BJ3+BJ10+BJ17)+2*(BK3+BK10+BK17)</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BK50" s="324"/>
     </row>
@@ -39177,7 +39333,7 @@
       <c r="BI51" s="324"/>
       <c r="BJ51" s="324">
         <f>(BJ6+BJ13+BJ20)+2*(BK6+BK13+BK20)</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BK51" s="324"/>
     </row>
@@ -39489,7 +39645,7 @@
       <c r="BI53" s="324"/>
       <c r="BJ53" s="324">
         <f>(BJ7+BJ14+BJ21)+2*(BK7+BK14+BK21)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK53" s="324"/>
     </row>
@@ -39674,119 +39830,119 @@
     </row>
     <row r="67" spans="32:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="32:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AF68" s="385">
-        <v>0</v>
-      </c>
-      <c r="AG68" s="385">
-        <v>0</v>
-      </c>
-      <c r="AH68" s="385">
+      <c r="AF68" s="346">
+        <v>10</v>
+      </c>
+      <c r="AG68" s="346">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="346">
         <v>2</v>
       </c>
-      <c r="AI68" s="385">
-        <v>0</v>
-      </c>
-      <c r="AJ68" s="385">
-        <v>0</v>
-      </c>
-      <c r="AK68" s="385">
+      <c r="AI68" s="346">
+        <v>10</v>
+      </c>
+      <c r="AJ68" s="346">
+        <v>1</v>
+      </c>
+      <c r="AK68" s="346">
+        <v>4</v>
+      </c>
+      <c r="AL68" s="347"/>
+      <c r="AM68" s="347">
+        <v>17</v>
+      </c>
+      <c r="AN68" s="347">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="347">
+        <v>35</v>
+      </c>
+      <c r="AP68" s="347">
+        <v>14</v>
+      </c>
+      <c r="AQ68" s="347">
+        <v>3</v>
+      </c>
+      <c r="AR68" s="347">
+        <v>28</v>
+      </c>
+      <c r="AS68" s="347"/>
+      <c r="AT68" s="346">
+        <v>7</v>
+      </c>
+      <c r="AU68" s="346">
+        <v>0</v>
+      </c>
+      <c r="AV68" s="346">
+        <v>1</v>
+      </c>
+      <c r="AW68" s="346">
         <v>6</v>
       </c>
-      <c r="AL68" s="386"/>
-      <c r="AM68" s="386">
-        <v>0</v>
-      </c>
-      <c r="AN68" s="386">
-        <v>0</v>
-      </c>
-      <c r="AO68" s="386">
-        <v>43</v>
-      </c>
-      <c r="AP68" s="386">
-        <v>0</v>
-      </c>
-      <c r="AQ68" s="386">
-        <v>0</v>
-      </c>
-      <c r="AR68" s="386">
-        <v>45</v>
-      </c>
-      <c r="AS68" s="386"/>
-      <c r="AT68" s="385">
-        <v>0</v>
-      </c>
-      <c r="AU68" s="385">
-        <v>0</v>
-      </c>
-      <c r="AV68" s="385">
+      <c r="AX68" s="346">
+        <v>0</v>
+      </c>
+      <c r="AY68" s="346">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="32:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AF69" s="346">
+        <v>2</v>
+      </c>
+      <c r="AG69" s="346">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="346">
+        <v>8</v>
+      </c>
+      <c r="AI69" s="346">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="346">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="346">
         <v>6</v>
       </c>
-      <c r="AW68" s="385">
-        <v>0</v>
-      </c>
-      <c r="AX68" s="385">
-        <v>0</v>
-      </c>
-      <c r="AY68" s="385">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="32:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AF69" s="385">
-        <v>0</v>
-      </c>
-      <c r="AG69" s="385">
-        <v>0</v>
-      </c>
-      <c r="AH69" s="385">
-        <v>1</v>
-      </c>
-      <c r="AI69" s="385">
-        <v>0</v>
-      </c>
-      <c r="AJ69" s="385">
-        <v>0</v>
-      </c>
-      <c r="AK69" s="385">
-        <v>0</v>
-      </c>
-      <c r="AL69" s="386"/>
-      <c r="AM69" s="386">
-        <v>0</v>
-      </c>
-      <c r="AN69" s="386">
-        <v>0</v>
-      </c>
-      <c r="AO69" s="386">
+      <c r="AL69" s="347"/>
+      <c r="AM69" s="347">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="347">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="347">
+        <v>26</v>
+      </c>
+      <c r="AP69" s="347">
         <v>2</v>
       </c>
-      <c r="AP69" s="386">
-        <v>0</v>
-      </c>
-      <c r="AQ69" s="386">
-        <v>0</v>
-      </c>
-      <c r="AR69" s="386">
-        <v>0</v>
-      </c>
-      <c r="AS69" s="386"/>
-      <c r="AT69" s="385">
-        <v>0</v>
-      </c>
-      <c r="AU69" s="385">
-        <v>0</v>
-      </c>
-      <c r="AV69" s="385">
-        <v>0</v>
-      </c>
-      <c r="AW69" s="385">
-        <v>0</v>
-      </c>
-      <c r="AX69" s="385">
-        <v>0</v>
-      </c>
-      <c r="AY69" s="385">
-        <v>0</v>
+      <c r="AQ69" s="347">
+        <v>0</v>
+      </c>
+      <c r="AR69" s="347">
+        <v>33</v>
+      </c>
+      <c r="AS69" s="347"/>
+      <c r="AT69" s="346">
+        <v>0</v>
+      </c>
+      <c r="AU69" s="346">
+        <v>0</v>
+      </c>
+      <c r="AV69" s="346">
+        <v>7</v>
+      </c>
+      <c r="AW69" s="346">
+        <v>0</v>
+      </c>
+      <c r="AX69" s="346">
+        <v>0</v>
+      </c>
+      <c r="AY69" s="346">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -40102,7 +40258,7 @@
       </c>
       <c r="AF5" s="95">
         <f>'Data Ocupacion'!BJ40</f>
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:32" s="85" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -40230,7 +40386,7 @@
       </c>
       <c r="AF6" s="95">
         <f>'Data Ocupacion'!BJ41</f>
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:32" s="85" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -40358,7 +40514,7 @@
       </c>
       <c r="AF7" s="95">
         <f>'Data Ocupacion'!BJ42</f>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:32" s="85" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -40486,7 +40642,7 @@
       </c>
       <c r="AF8" s="95">
         <f>'Data Ocupacion'!BJ43</f>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:32" s="85" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -40742,7 +40898,7 @@
       </c>
       <c r="AF10" s="95">
         <f>'Data Ocupacion'!BJ45</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:32" s="85" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -40898,7 +41054,7 @@
       </c>
       <c r="AF12" s="95">
         <f>'Data Ocupacion'!BJ48</f>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:32" s="85" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -41026,7 +41182,7 @@
       </c>
       <c r="AF13" s="95">
         <f>'Data Ocupacion'!BJ49</f>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:32" s="85" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -41154,7 +41310,7 @@
       </c>
       <c r="AF14" s="95">
         <f>'Data Ocupacion'!BJ50</f>
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:32" s="85" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -41282,7 +41438,7 @@
       </c>
       <c r="AF15" s="95">
         <f>'Data Ocupacion'!BJ51</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:32" s="85" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -41410,7 +41566,7 @@
       </c>
       <c r="AF16" s="95">
         <f>'Data Ocupacion'!BJ53</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:32" s="85" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -41668,7 +41824,7 @@
       </c>
       <c r="AF19" s="83">
         <f>'KM-Servicio'!Q208</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -42027,7 +42183,7 @@
         <v>0</v>
       </c>
       <c r="AF22" s="83">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -42184,7 +42340,7 @@
       </c>
       <c r="B27" s="226">
         <f t="shared" ref="B27:B34" si="0">SUM(C27:AF27)</f>
-        <v>5720</v>
+        <v>5949</v>
       </c>
       <c r="C27" s="91">
         <f t="shared" ref="C27:AD27" si="1">SUM(C5:C10)</f>
@@ -42304,7 +42460,7 @@
       </c>
       <c r="AF27" s="91">
         <f t="shared" ref="AF27" si="3">SUM(AF5:AF10)</f>
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
@@ -42313,7 +42469,7 @@
       </c>
       <c r="B28" s="226">
         <f t="shared" si="0"/>
-        <v>7486</v>
+        <v>7802</v>
       </c>
       <c r="C28" s="91">
         <f t="shared" ref="C28:AD28" si="4">SUM(C12:C17)</f>
@@ -42433,7 +42589,7 @@
       </c>
       <c r="AF28" s="91">
         <f t="shared" ref="AF28" si="6">SUM(AF12:AF17)</f>
-        <v>0</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.25">
@@ -42442,7 +42598,7 @@
       </c>
       <c r="B29" s="226">
         <f t="shared" si="0"/>
-        <v>298757.06000000006</v>
+        <v>311245.17000000004</v>
       </c>
       <c r="C29" s="91">
         <f>(C12*$B$12+C13*$B$13+C14*$B$14+C15*$B$15+C17*$B$17+C20*$B$20+C16*$B$16+C19*$B$19+C22*$B$22+C23*$B$23+C21*B21)</f>
@@ -42562,7 +42718,7 @@
       </c>
       <c r="AF29" s="91">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12488.11</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
@@ -42571,7 +42727,7 @@
       </c>
       <c r="B30" s="226">
         <f t="shared" si="0"/>
-        <v>226263.7699999999</v>
+        <v>235116.25999999989</v>
       </c>
       <c r="C30" s="91">
         <f t="shared" ref="C30:AD30" si="9">$B$5*C5+$B$6*C6+$B$7*C7+$B$8*C8+$B$10*C10+$B$9*C9</f>
@@ -42691,7 +42847,7 @@
       </c>
       <c r="AF30" s="91">
         <f t="shared" ref="AF30" si="11">$B$5*AF5+$B$6*AF6+$B$7*AF7+$B$8*AF8+$B$10*AF10+$B$9*AF9</f>
-        <v>0</v>
+        <v>8852.49</v>
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
@@ -42700,7 +42856,7 @@
       </c>
       <c r="B31" s="226">
         <f t="shared" si="0"/>
-        <v>31070734.24000001</v>
+        <v>32369497.680000011</v>
       </c>
       <c r="C31" s="91">
         <f t="shared" ref="C31:AD31" si="12">C29*104</f>
@@ -42820,7 +42976,7 @@
       </c>
       <c r="AF31" s="91">
         <f t="shared" ref="AF31" si="14">AF29*104</f>
-        <v>0</v>
+        <v>1298763.44</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
@@ -42829,7 +42985,7 @@
       </c>
       <c r="B32" s="89">
         <f t="shared" si="0"/>
-        <v>597514.12000000011</v>
+        <v>622490.34000000008</v>
       </c>
       <c r="C32" s="91">
         <f>C29*2</f>
@@ -42949,7 +43105,7 @@
       </c>
       <c r="AF32" s="91">
         <f t="shared" ref="AF32" si="17">AF29*2</f>
-        <v>0</v>
+        <v>24976.22</v>
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
@@ -42958,7 +43114,7 @@
       </c>
       <c r="B33" s="89">
         <f t="shared" si="0"/>
-        <v>2709932</v>
+        <v>2824324</v>
       </c>
       <c r="C33" s="91">
         <f>+C28*362</f>
@@ -43078,7 +43234,7 @@
       </c>
       <c r="AF33" s="91">
         <f t="shared" ref="AF33" si="20">+AF28*362</f>
-        <v>0</v>
+        <v>114392</v>
       </c>
     </row>
     <row r="34" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -43087,7 +43243,7 @@
       </c>
       <c r="B34" s="226">
         <f t="shared" si="0"/>
-        <v>23691434.85800001</v>
+        <v>24681741.98100001</v>
       </c>
       <c r="C34" s="91">
         <f>C29*79.3</f>
@@ -43207,7 +43363,7 @@
       </c>
       <c r="AF34" s="91">
         <f t="shared" ref="AF34" si="23">AF29*79.3</f>
-        <v>0</v>
+        <v>990307.12300000002</v>
       </c>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.25">
@@ -43521,19 +43677,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="373" t="s">
+      <c r="A2" s="375" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="374"/>
-      <c r="C2" s="374"/>
-      <c r="D2" s="374"/>
-      <c r="E2" s="374"/>
-      <c r="F2" s="374"/>
-      <c r="G2" s="374"/>
-      <c r="H2" s="374"/>
-      <c r="I2" s="374"/>
-      <c r="J2" s="374"/>
-      <c r="K2" s="374"/>
+      <c r="B2" s="376"/>
+      <c r="C2" s="376"/>
+      <c r="D2" s="376"/>
+      <c r="E2" s="376"/>
+      <c r="F2" s="376"/>
+      <c r="G2" s="376"/>
+      <c r="H2" s="376"/>
+      <c r="I2" s="376"/>
+      <c r="J2" s="376"/>
+      <c r="K2" s="376"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="158" t="s">
@@ -44793,19 +44949,19 @@
       </c>
       <c r="B33" s="312">
         <f>'KM-Servicio'!N214</f>
-        <v>-63937011</v>
+        <v>12797</v>
       </c>
       <c r="C33" s="312">
         <f t="shared" si="0"/>
-        <v>-63627988</v>
+        <v>321820</v>
       </c>
       <c r="D33" s="12">
         <f>'KM-Servicio'!W214</f>
-        <v>0</v>
+        <v>12488.110000000002</v>
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>298757.06000000006</v>
+        <v>311245.17000000004</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -44817,11 +44973,11 @@
       </c>
       <c r="H33" s="167">
         <f>'KM-Servicio'!D214+'KM-Servicio'!E214</f>
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="I33" s="12">
         <f>'Oferta Diaria'!AF34</f>
-        <v>0</v>
+        <v>990307.12300000002</v>
       </c>
       <c r="J33" s="161" t="s">
         <v>137</v>
@@ -44869,19 +45025,19 @@
       </c>
       <c r="B36" s="169">
         <f>SUM(B4:B34)</f>
-        <v>-63627988</v>
+        <v>321820</v>
       </c>
       <c r="C36" s="169">
         <f>SUM(C4:C34)</f>
-        <v>-58767969</v>
+        <v>5181839</v>
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>298757.06000000006</v>
+        <v>311245.17000000004</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4989348.040000001</v>
+        <v>5001836.1500000004</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
@@ -44893,11 +45049,11 @@
       </c>
       <c r="H36" s="169">
         <f>SUM(H4:H34)</f>
-        <v>5720</v>
+        <v>5949</v>
       </c>
       <c r="I36" s="169">
         <f>SUM(I4:I34)</f>
-        <v>23691434.85800001</v>
+        <v>24681741.98100001</v>
       </c>
       <c r="J36" s="30"/>
       <c r="K36" s="168"/>
@@ -44929,12 +45085,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="375" t="s">
+      <c r="A3" s="377" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="376"/>
-      <c r="C3" s="376"/>
-      <c r="D3" s="377"/>
+      <c r="B3" s="378"/>
+      <c r="C3" s="378"/>
+      <c r="D3" s="379"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -44956,11 +45112,11 @@
       </c>
       <c r="B5" s="129">
         <f>C5/30</f>
-        <v>249.53333333333333</v>
+        <v>260.06666666666666</v>
       </c>
       <c r="C5" s="130">
         <f>'KM-Servicio'!J239</f>
-        <v>7486</v>
+        <v>7802</v>
       </c>
       <c r="D5" s="130">
         <f>'KM-Servicio'!C234</f>
@@ -44973,11 +45129,11 @@
       </c>
       <c r="B6" s="129">
         <f>C6/30</f>
-        <v>190.66666666666666</v>
+        <v>198.3</v>
       </c>
       <c r="C6" s="130">
         <f>'KM-Servicio'!K232</f>
-        <v>5720</v>
+        <v>5949</v>
       </c>
       <c r="D6" s="130">
         <f>'KM-Servicio'!D232</f>
@@ -44990,11 +45146,11 @@
       </c>
       <c r="B7" s="129">
         <f>C7/30</f>
-        <v>10027.768999999998</v>
+        <v>10446.059666666666</v>
       </c>
       <c r="C7" s="130">
         <f>'KM-Servicio'!M232</f>
-        <v>300833.06999999995</v>
+        <v>313381.78999999998</v>
       </c>
       <c r="D7" s="130">
         <f>'KM-Servicio'!F232</f>
@@ -45007,11 +45163,11 @@
       </c>
       <c r="B8" s="129">
         <f>C8/30</f>
-        <v>7542.1256666666677</v>
+        <v>7837.2086666666673</v>
       </c>
       <c r="C8" s="130">
         <f>'KM-Servicio'!L232</f>
-        <v>226263.77000000002</v>
+        <v>235116.26</v>
       </c>
       <c r="D8" s="130">
         <f>'KM-Servicio'!E232</f>
@@ -45024,11 +45180,11 @@
       </c>
       <c r="B9" s="129">
         <f>C9/30</f>
-        <v>1042887.9759999999</v>
+        <v>1086390.2053333332</v>
       </c>
       <c r="C9" s="130">
         <f>'KM-Servicio'!N232</f>
-        <v>31286639.279999997</v>
+        <v>32591706.16</v>
       </c>
       <c r="D9" s="130">
         <f>'KM-Servicio'!G232</f>
@@ -45080,12 +45236,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="378" t="s">
+      <c r="A13" s="380" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="379"/>
-      <c r="C13" s="379"/>
-      <c r="D13" s="380"/>
+      <c r="B13" s="381"/>
+      <c r="C13" s="381"/>
+      <c r="D13" s="382"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -45132,8 +45288,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="384"/>
-      <c r="H16" s="384"/>
+      <c r="G16" s="386"/>
+      <c r="H16" s="386"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -45148,8 +45304,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="384"/>
-      <c r="H17" s="384"/>
+      <c r="G17" s="386"/>
+      <c r="H17" s="386"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -45164,8 +45320,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="384"/>
-      <c r="H18" s="384"/>
+      <c r="G18" s="386"/>
+      <c r="H18" s="386"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -45179,8 +45335,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="384"/>
-      <c r="H19" s="384"/>
+      <c r="G19" s="386"/>
+      <c r="H19" s="386"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -45194,8 +45350,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="384"/>
-      <c r="H20" s="384"/>
+      <c r="G20" s="386"/>
+      <c r="H20" s="386"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -45209,8 +45365,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="384"/>
-      <c r="H21" s="384"/>
+      <c r="G21" s="386"/>
+      <c r="H21" s="386"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -45235,9 +45391,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="381"/>
-      <c r="C23" s="382"/>
-      <c r="D23" s="383"/>
+      <c r="B23" s="383"/>
+      <c r="C23" s="384"/>
+      <c r="D23" s="385"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -45249,10 +45405,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="378"/>
-      <c r="B24" s="379"/>
-      <c r="C24" s="379"/>
-      <c r="D24" s="380"/>
+      <c r="A24" s="380"/>
+      <c r="B24" s="381"/>
+      <c r="C24" s="381"/>
+      <c r="D24" s="382"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -45365,9 +45521,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="381"/>
-      <c r="C34" s="382"/>
-      <c r="D34" s="383"/>
+      <c r="B34" s="383"/>
+      <c r="C34" s="384"/>
+      <c r="D34" s="385"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -45787,13 +45943,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CDF204E-0F69-48BF-B55D-4AA794A69F79}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DF91B3B-11FD-4CE6-AB15-848CF5215DBE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015359CB-7DF5-43D5-A22D-803017E8B905}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669151E9-FF4A-44C4-A4C1-BC22018F50CD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7581C8-F14F-44A7-BCB9-28C305E1109E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE50111-D01F-48FD-ADC2-456C6B7A1B05}"/>
 </file>
--- a/data/umr/Resumen UMR Junio 2026.xlsx
+++ b/data/umr/Resumen UMR Junio 2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6FD30B-F375-45DA-8AE3-7D69E6725542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{DE6FD30B-F375-45DA-8AE3-7D69E6725542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE5DCD5E-0EEB-4712-81DD-91D968A076AC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Odometro-Kilometraje" sheetId="1" r:id="rId1"/>
@@ -1252,7 +1252,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="188">
   <si>
     <t>Control Contador Kilometraje de Trenes</t>
   </si>
@@ -1813,6 +1813,9 @@
   </si>
   <si>
     <t>Estación Puerto. Servicio 423 (viaje 64) es suprimido por falla del servicio 601.</t>
+  </si>
+  <si>
+    <t>ojo</t>
   </si>
 </sst>
 </file>
@@ -5739,7 +5742,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AH93"/>
+  <dimension ref="A1:BK93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -13966,7 +13969,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="81" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
         <v>114</v>
       </c>
@@ -14090,7 +14093,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="82" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
         <v>115</v>
       </c>
@@ -14214,7 +14217,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="83" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>116</v>
       </c>
@@ -14338,7 +14341,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="84" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
         <v>117</v>
       </c>
@@ -14462,7 +14465,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="85" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
         <v>118</v>
       </c>
@@ -14586,7 +14589,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="86" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="328" t="s">
         <v>177</v>
       </c>
@@ -14709,8 +14712,98 @@
         <f t="shared" si="71"/>
         <v>86</v>
       </c>
-    </row>
-    <row r="87" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AH86" s="124">
+        <v>260</v>
+      </c>
+      <c r="AI86" s="124">
+        <v>259</v>
+      </c>
+      <c r="AJ86" s="124">
+        <v>259</v>
+      </c>
+      <c r="AK86" s="124">
+        <v>178</v>
+      </c>
+      <c r="AL86" s="124">
+        <v>211</v>
+      </c>
+      <c r="AM86" s="124">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="124">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="124">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="124">
+        <v>346</v>
+      </c>
+      <c r="AQ86" s="124">
+        <v>346</v>
+      </c>
+      <c r="AR86" s="124">
+        <v>264</v>
+      </c>
+      <c r="AS86" s="124">
+        <v>210</v>
+      </c>
+      <c r="AT86" s="124">
+        <v>0</v>
+      </c>
+      <c r="AU86" s="124">
+        <v>0</v>
+      </c>
+      <c r="AV86" s="124">
+        <v>261</v>
+      </c>
+      <c r="AW86" s="124">
+        <v>260</v>
+      </c>
+      <c r="AX86" s="124">
+        <v>0</v>
+      </c>
+      <c r="AY86" s="124">
+        <v>211</v>
+      </c>
+      <c r="AZ86" s="124">
+        <v>86</v>
+      </c>
+      <c r="BA86" s="124">
+        <v>0</v>
+      </c>
+      <c r="BB86" s="124">
+        <v>0</v>
+      </c>
+      <c r="BC86" s="124">
+        <v>262</v>
+      </c>
+      <c r="BD86" s="124">
+        <v>260</v>
+      </c>
+      <c r="BE86" s="124">
+        <v>262</v>
+      </c>
+      <c r="BF86" s="124">
+        <v>211</v>
+      </c>
+      <c r="BG86" s="124">
+        <v>260</v>
+      </c>
+      <c r="BH86" s="124">
+        <v>0</v>
+      </c>
+      <c r="BI86" s="124">
+        <v>0</v>
+      </c>
+      <c r="BJ86" s="124">
+        <v>0</v>
+      </c>
+      <c r="BK86" s="124">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="14"/>
       <c r="B87" s="172"/>
       <c r="E87" s="124"/>
@@ -14739,7 +14832,7 @@
       <c r="AB87" s="124"/>
       <c r="AC87" s="124"/>
     </row>
-    <row r="88" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="15" t="s">
         <v>34</v>
       </c>
@@ -14864,7 +14957,7 @@
         <v>12797</v>
       </c>
     </row>
-    <row r="89" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="240"/>
       <c r="B89" s="241"/>
       <c r="C89" s="241"/>
@@ -14895,7 +14988,7 @@
       <c r="AB89" s="241"/>
       <c r="AC89" s="241"/>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A90" s="326" t="s">
         <v>176</v>
       </c>
@@ -15019,7 +15112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="326" t="s">
         <v>178</v>
       </c>
@@ -15135,7 +15228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="326" t="s">
         <v>179</v>
       </c>
@@ -15259,7 +15352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:31" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:63" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="328" t="s">
         <v>180</v>
       </c>
@@ -19467,7 +19560,7 @@
         <v>229</v>
       </c>
       <c r="J60" s="120">
-        <f t="shared" si="47"/>
+        <f>SUM(J54:J59)</f>
         <v>12520.68</v>
       </c>
       <c r="K60" s="119">
@@ -19505,6 +19598,7 @@
         <f>SUM(X54:X59)</f>
         <v>12606.940000000002</v>
       </c>
+      <c r="Y60" s="198"/>
     </row>
     <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" s="60">
@@ -26253,12 +26347,14 @@
       <c r="Q160" s="186"/>
       <c r="R160" s="186"/>
       <c r="S160" s="217"/>
-      <c r="T160" s="183"/>
+      <c r="T160" s="183">
+        <v>2</v>
+      </c>
       <c r="U160" s="217"/>
       <c r="V160" s="229"/>
       <c r="W160" s="185">
         <f>J160-(T160*($M$2-$K$1)+(U160*($M$2-$M$1)))</f>
-        <v>5175.6000000000004</v>
+        <v>5140.1400000000003</v>
       </c>
       <c r="X160" s="182">
         <f>H160*$M$2</f>
@@ -26267,7 +26363,9 @@
       <c r="Y160" s="172"/>
     </row>
     <row r="161" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="276"/>
+      <c r="A161" s="276" t="s">
+        <v>187</v>
+      </c>
       <c r="B161" s="295">
         <v>33</v>
       </c>
@@ -26581,7 +26679,7 @@
       </c>
       <c r="O165" s="21">
         <f>(W165/N165)*100</f>
-        <v>96.621868756723543</v>
+        <v>96.34939296142619</v>
       </c>
       <c r="P165" s="192"/>
       <c r="Q165" s="181"/>
@@ -26592,7 +26690,7 @@
       <c r="V165" s="181"/>
       <c r="W165" s="193">
         <f>SUM(W159:W164)</f>
-        <v>12574.370000000003</v>
+        <v>12538.910000000003</v>
       </c>
       <c r="X165" s="193">
         <f>SUM(X159:X164)</f>
@@ -29544,12 +29642,14 @@
       <c r="Q209" s="186"/>
       <c r="R209" s="186"/>
       <c r="S209" s="186"/>
-      <c r="T209" s="183"/>
+      <c r="T209" s="183">
+        <v>1</v>
+      </c>
       <c r="U209" s="183"/>
       <c r="V209" s="206"/>
       <c r="W209" s="185">
         <f>J209-(T209*($M$2-$K$1)+(U209*($M$2-$M$1)))</f>
-        <v>5175.6000000000004</v>
+        <v>5157.8700000000008</v>
       </c>
       <c r="X209" s="182">
         <f>H209*$M$2</f>
@@ -29557,7 +29657,9 @@
       </c>
     </row>
     <row r="210" spans="1:28" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="202"/>
+      <c r="A210" s="202" t="s">
+        <v>187</v>
+      </c>
       <c r="B210" s="295">
         <v>33</v>
       </c>
@@ -29871,7 +29973,7 @@
       </c>
       <c r="O214" s="21">
         <f>(W214/N214)*100</f>
-        <v>97.586231147925318</v>
+        <v>97.447683050715028</v>
       </c>
       <c r="P214" s="192"/>
       <c r="Q214" s="181"/>
@@ -29882,7 +29984,7 @@
       <c r="V214" s="181"/>
       <c r="W214" s="193">
         <f>SUM(W208:W213)</f>
-        <v>12488.110000000002</v>
+        <v>12470.380000000003</v>
       </c>
       <c r="X214" s="193">
         <f>SUM(X208:X213)</f>
@@ -30537,7 +30639,7 @@
       </c>
       <c r="T225" s="209">
         <f>SUM(T194,T187,T180,T173,T166,T159,T152,T145,T138,T131,T124,T117,T110,T103,T96,T89,T82,T75,T68,T61,T54,T47,T40,T33,T26,T19,T12,T5,T201,T208,T215)+T6+T13+T20+T27+T34+T41+T48+T55+T62+T69+T76+T83+T90+T97+T104+T111+T118+T125+T132+T139+T146+T153+T160+T167+T174+T181+T188+T195+T202+T209+T216</f>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U225" s="209">
         <f>SUM(U194,U187,U180,U173,U166,U159,U152,U145,U138,U131,U124,U117,U110,U103,U96,U89,U82,U75,U68,U61,U54,U47,U40,U33,U26,U19,U12,U5,U201,U208,U216)</f>
@@ -30549,7 +30651,7 @@
       </c>
       <c r="W225" s="231">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214</f>
-        <v>311245.17000000004</v>
+        <v>311191.98000000004</v>
       </c>
       <c r="X225" s="231">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214</f>
@@ -41924,7 +42026,7 @@
       </c>
       <c r="Y20" s="83">
         <f>'KM-Servicio'!T160</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z20" s="83">
         <f>'KM-Servicio'!T167</f>
@@ -41952,7 +42054,7 @@
       </c>
       <c r="AF20" s="83">
         <f>'KM-Servicio'!T209</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
@@ -42598,7 +42700,7 @@
       </c>
       <c r="B29" s="226">
         <f t="shared" si="0"/>
-        <v>311245.17000000004</v>
+        <v>311191.98000000004</v>
       </c>
       <c r="C29" s="91">
         <f>(C12*$B$12+C13*$B$13+C14*$B$14+C15*$B$15+C17*$B$17+C20*$B$20+C16*$B$16+C19*$B$19+C22*$B$22+C23*$B$23+C21*B21)</f>
@@ -42690,7 +42792,7 @@
       </c>
       <c r="Y29" s="91">
         <f t="shared" si="7"/>
-        <v>12574.370000000003</v>
+        <v>12538.910000000003</v>
       </c>
       <c r="Z29" s="91">
         <f t="shared" si="7"/>
@@ -42718,7 +42820,7 @@
       </c>
       <c r="AF29" s="91">
         <f t="shared" si="8"/>
-        <v>12488.11</v>
+        <v>12470.380000000001</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
@@ -42856,7 +42958,7 @@
       </c>
       <c r="B31" s="226">
         <f t="shared" si="0"/>
-        <v>32369497.680000011</v>
+        <v>32363965.920000009</v>
       </c>
       <c r="C31" s="91">
         <f t="shared" ref="C31:AD31" si="12">C29*104</f>
@@ -42948,7 +43050,7 @@
       </c>
       <c r="Y31" s="91">
         <f t="shared" si="12"/>
-        <v>1307734.4800000002</v>
+        <v>1304046.6400000004</v>
       </c>
       <c r="Z31" s="91">
         <f t="shared" si="12"/>
@@ -42976,7 +43078,7 @@
       </c>
       <c r="AF31" s="91">
         <f t="shared" ref="AF31" si="14">AF29*104</f>
-        <v>1298763.44</v>
+        <v>1296919.52</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
@@ -42985,7 +43087,7 @@
       </c>
       <c r="B32" s="89">
         <f t="shared" si="0"/>
-        <v>622490.34000000008</v>
+        <v>622383.96000000008</v>
       </c>
       <c r="C32" s="91">
         <f>C29*2</f>
@@ -43077,7 +43179,7 @@
       </c>
       <c r="Y32" s="91">
         <f t="shared" si="15"/>
-        <v>25148.740000000005</v>
+        <v>25077.820000000007</v>
       </c>
       <c r="Z32" s="91">
         <f t="shared" si="15"/>
@@ -43105,7 +43207,7 @@
       </c>
       <c r="AF32" s="91">
         <f t="shared" ref="AF32" si="17">AF29*2</f>
-        <v>24976.22</v>
+        <v>24940.760000000002</v>
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
@@ -43243,7 +43345,7 @@
       </c>
       <c r="B34" s="226">
         <f t="shared" si="0"/>
-        <v>24681741.98100001</v>
+        <v>24677524.01400001</v>
       </c>
       <c r="C34" s="91">
         <f>C29*79.3</f>
@@ -43335,7 +43437,7 @@
       </c>
       <c r="Y34" s="91">
         <f t="shared" si="21"/>
-        <v>997147.5410000002</v>
+        <v>994335.5630000002</v>
       </c>
       <c r="Z34" s="91">
         <f t="shared" si="21"/>
@@ -43363,7 +43465,7 @@
       </c>
       <c r="AF34" s="91">
         <f t="shared" ref="AF34" si="23">AF29*79.3</f>
-        <v>990307.12300000002</v>
+        <v>988901.13400000008</v>
       </c>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.25">
@@ -44663,15 +44765,15 @@
       </c>
       <c r="D26" s="12">
         <f>'KM-Servicio'!$W$165</f>
-        <v>12574.370000000003</v>
+        <v>12538.910000000003</v>
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>245206.56000000006</v>
+        <v>245171.10000000006</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O165</f>
-        <v>96.621868756723543</v>
+        <v>96.34939296142619</v>
       </c>
       <c r="G26" s="167">
         <f>SUM('KM-Servicio'!B165:C165)</f>
@@ -44683,7 +44785,7 @@
       </c>
       <c r="I26" s="12">
         <f>'Oferta Diaria'!Y34</f>
-        <v>997147.5410000002</v>
+        <v>994335.5630000002</v>
       </c>
       <c r="J26" s="161" t="s">
         <v>137</v>
@@ -44709,7 +44811,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>257590.68000000005</v>
+        <v>257555.22000000006</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O172</f>
@@ -44751,7 +44853,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>269997.56000000006</v>
+        <v>269962.10000000003</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O179</f>
@@ -44793,7 +44895,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>282453.92000000004</v>
+        <v>282418.46000000002</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O186</f>
@@ -44835,7 +44937,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>288923.42000000004</v>
+        <v>288887.96000000002</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O193</f>
@@ -44877,7 +44979,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>293840.24000000005</v>
+        <v>293804.78000000003</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O200</f>
@@ -44919,7 +45021,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>298757.06000000006</v>
+        <v>298721.60000000003</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O207</f>
@@ -44957,11 +45059,11 @@
       </c>
       <c r="D33" s="12">
         <f>'KM-Servicio'!W214</f>
-        <v>12488.110000000002</v>
+        <v>12470.380000000003</v>
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>311245.17000000004</v>
+        <v>311191.98000000004</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -44977,7 +45079,7 @@
       </c>
       <c r="I33" s="12">
         <f>'Oferta Diaria'!AF34</f>
-        <v>990307.12300000002</v>
+        <v>988901.13400000008</v>
       </c>
       <c r="J33" s="161" t="s">
         <v>137</v>
@@ -45033,15 +45135,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>311245.17000000004</v>
+        <v>311191.98000000004</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>5001836.1500000004</v>
+        <v>5001534.7400000012</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>97.098024983425589</v>
+        <v>97.088942456915674</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -45053,7 +45155,7 @@
       </c>
       <c r="I36" s="169">
         <f>SUM(I4:I34)</f>
-        <v>24681741.98100001</v>
+        <v>24677524.01400001</v>
       </c>
       <c r="J36" s="30"/>
       <c r="K36" s="168"/>
@@ -45674,6 +45776,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -45920,36 +46044,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DF91B3B-11FD-4CE6-AB15-848CF5215DBE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669151E9-FF4A-44C4-A4C1-BC22018F50CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669151E9-FF4A-44C4-A4C1-BC22018F50CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE50111-D01F-48FD-ADC2-456C6B7A1B05}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE50111-D01F-48FD-ADC2-456C6B7A1B05}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DF91B3B-11FD-4CE6-AB15-848CF5215DBE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/umr/Resumen UMR Junio 2026.xlsx
+++ b/data/umr/Resumen UMR Junio 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{DE6FD30B-F375-45DA-8AE3-7D69E6725542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE5DCD5E-0EEB-4712-81DD-91D968A076AC}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{DE6FD30B-F375-45DA-8AE3-7D69E6725542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCDEE732-FFAF-4874-935C-6F439735A4C1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4636,7 +4636,28 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4683,27 +4704,6 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4716,6 +4716,9 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4743,9 +4746,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -15610,14 +15610,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="371" t="s">
+      <c r="B2" s="350" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="372" t="s">
+      <c r="C2" s="350"/>
+      <c r="D2" s="351" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="372"/>
+      <c r="E2" s="351"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -15701,59 +15701,59 @@
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="371" t="s">
+      <c r="B3" s="350" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="371"/>
-      <c r="D3" s="372" t="s">
+      <c r="C3" s="350"/>
+      <c r="D3" s="351" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="372"/>
-      <c r="F3" s="350" t="s">
+      <c r="E3" s="351"/>
+      <c r="F3" s="355" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="350" t="s">
+      <c r="G3" s="355" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="350" t="s">
+      <c r="H3" s="355" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="350" t="s">
+      <c r="I3" s="355" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="350" t="s">
+      <c r="J3" s="355" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="350" t="s">
+      <c r="K3" s="355" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="350" t="s">
+      <c r="L3" s="355" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="350" t="s">
+      <c r="M3" s="355" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="357" t="s">
+      <c r="N3" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="364" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="356"/>
-      <c r="Q3" s="358" t="s">
+      <c r="P3" s="363"/>
+      <c r="Q3" s="365" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="359"/>
-      <c r="S3" s="360"/>
-      <c r="T3" s="361" t="s">
+      <c r="R3" s="366"/>
+      <c r="S3" s="367"/>
+      <c r="T3" s="368" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="362"/>
-      <c r="V3" s="363"/>
-      <c r="W3" s="354" t="s">
+      <c r="U3" s="369"/>
+      <c r="V3" s="370"/>
+      <c r="W3" s="361" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="354" t="s">
+      <c r="X3" s="361" t="s">
         <v>162</v>
       </c>
     </row>
@@ -15771,17 +15771,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="350"/>
-      <c r="G4" s="351"/>
-      <c r="H4" s="351"/>
-      <c r="I4" s="350"/>
-      <c r="J4" s="350"/>
-      <c r="K4" s="350"/>
-      <c r="L4" s="350"/>
-      <c r="M4" s="350"/>
-      <c r="N4" s="357"/>
-      <c r="O4" s="357"/>
-      <c r="P4" s="356"/>
+      <c r="F4" s="355"/>
+      <c r="G4" s="358"/>
+      <c r="H4" s="358"/>
+      <c r="I4" s="355"/>
+      <c r="J4" s="355"/>
+      <c r="K4" s="355"/>
+      <c r="L4" s="355"/>
+      <c r="M4" s="355"/>
+      <c r="N4" s="364"/>
+      <c r="O4" s="364"/>
+      <c r="P4" s="363"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -15800,8 +15800,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="355"/>
-      <c r="X4" s="355"/>
+      <c r="W4" s="362"/>
+      <c r="X4" s="362"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -27222,7 +27222,7 @@
       <c r="O173" s="19"/>
       <c r="P173" s="146"/>
       <c r="Q173" s="183">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R173" s="183"/>
       <c r="S173" s="206"/>
@@ -27231,7 +27231,7 @@
       <c r="V173" s="228"/>
       <c r="W173" s="182">
         <f>J173-(Q173*($M$2-$K$1))-(R173*($M$2-$M$1))- (S173*($M$2-$I$2))+ (T173*($G$2))</f>
-        <v>5079.2800000000007</v>
+        <v>5097.01</v>
       </c>
       <c r="X173" s="182">
         <f>H173*$M$2</f>
@@ -27357,7 +27357,7 @@
       <c r="O175" s="19"/>
       <c r="P175" s="146"/>
       <c r="Q175" s="244">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R175" s="190"/>
       <c r="S175" s="228"/>
@@ -27366,7 +27366,7 @@
       <c r="V175" s="189"/>
       <c r="W175" s="182">
         <f>J175-(Q175*($M$1-$K$1))</f>
-        <v>1127.8699999999999</v>
+        <v>1124.1599999999999</v>
       </c>
       <c r="X175" s="182">
         <f>H175*$M$1</f>
@@ -27621,7 +27621,7 @@
       </c>
       <c r="O179" s="21">
         <f>(W179/N179)*100</f>
-        <v>96.065660085172283</v>
+        <v>96.174216027874564</v>
       </c>
       <c r="P179" s="192"/>
       <c r="Q179" s="181"/>
@@ -27632,7 +27632,7 @@
       <c r="V179" s="181"/>
       <c r="W179" s="193">
         <f>SUM(W173:W178)</f>
-        <v>12406.880000000001</v>
+        <v>12420.900000000001</v>
       </c>
       <c r="X179" s="193">
         <f>SUM(X173:X178)</f>
@@ -30467,38 +30467,38 @@
     <row r="222" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="223" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223"/>
-      <c r="B223" s="366" t="s">
+      <c r="B223" s="352" t="s">
         <v>56</v>
       </c>
-      <c r="C223" s="367"/>
-      <c r="D223" s="367"/>
-      <c r="E223" s="367"/>
-      <c r="F223" s="367"/>
-      <c r="G223" s="368"/>
+      <c r="C223" s="353"/>
+      <c r="D223" s="353"/>
+      <c r="E223" s="353"/>
+      <c r="F223" s="353"/>
+      <c r="G223" s="354"/>
       <c r="H223" s="290"/>
-      <c r="I223" s="366" t="s">
+      <c r="I223" s="352" t="s">
         <v>57</v>
       </c>
-      <c r="J223" s="367"/>
-      <c r="K223" s="367"/>
-      <c r="L223" s="367"/>
-      <c r="M223" s="367"/>
-      <c r="N223" s="368"/>
-      <c r="P223" s="364" t="s">
+      <c r="J223" s="353"/>
+      <c r="K223" s="353"/>
+      <c r="L223" s="353"/>
+      <c r="M223" s="353"/>
+      <c r="N223" s="354"/>
+      <c r="P223" s="371" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="364"/>
-      <c r="R223" s="364"/>
-      <c r="S223" s="365"/>
-      <c r="T223" s="361" t="s">
+      <c r="Q223" s="371"/>
+      <c r="R223" s="371"/>
+      <c r="S223" s="372"/>
+      <c r="T223" s="368" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="362"/>
-      <c r="V223" s="363"/>
-      <c r="W223" s="352" t="s">
+      <c r="U223" s="369"/>
+      <c r="V223" s="370"/>
+      <c r="W223" s="359" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="352" t="s">
+      <c r="X223" s="359" t="s">
         <v>162</v>
       </c>
     </row>
@@ -30564,8 +30564,8 @@
       <c r="V224" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="353"/>
-      <c r="X224" s="353"/>
+      <c r="W224" s="360"/>
+      <c r="X224" s="360"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -30623,7 +30623,7 @@
       <c r="O225" s="124"/>
       <c r="P225" s="209">
         <f>SUM(Q194,Q187,Q180,Q173,Q166,Q159,Q152,Q145,Q138,Q131,Q124,Q117,Q110,Q103,Q96,Q89,Q82,Q75,Q68,Q61,Q54,Q47,Q40,Q33,Q26,Q19,Q12,Q5,Q201,Q208,Q215)</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q225" s="209">
         <f>SUM(R194,R187,R180,R173,R166,R159,R152,R145,R138,R131,R124,R117,R110,R103,R96,R89,R82,R75,R68,R61,R54,R47,R40,R33,R26,R19,R12,R5,R201,R208,R215)</f>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="W225" s="231">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214</f>
-        <v>311191.98000000004</v>
+        <v>311206.00000000006</v>
       </c>
       <c r="X225" s="231">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214</f>
@@ -31075,10 +31075,10 @@
     </row>
     <row r="235" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A235" s="24"/>
-      <c r="B235" s="369" t="s">
+      <c r="B235" s="356" t="s">
         <v>55</v>
       </c>
-      <c r="C235" s="370"/>
+      <c r="C235" s="357"/>
       <c r="D235" s="25" t="s">
         <v>65</v>
       </c>
@@ -31254,18 +31254,6 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="28">
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="I223:N223"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="B235:C235"/>
-    <mergeCell ref="B223:G223"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
     <mergeCell ref="A83:A86"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
@@ -31282,6 +31270,18 @@
     <mergeCell ref="P223:S223"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
+    <mergeCell ref="I223:N223"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B235:C235"/>
+    <mergeCell ref="B223:G223"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="D187:E192 D180:E185 D173:E178 D194:E199">
     <cfRule type="expression" dxfId="46" priority="174">
@@ -40049,21 +40049,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -40080,6 +40065,21 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -41906,7 +41906,7 @@
       </c>
       <c r="AA19" s="83">
         <f>'KM-Servicio'!Q173</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB19" s="83">
         <f>'KM-Servicio'!Q180</f>
@@ -42700,7 +42700,7 @@
       </c>
       <c r="B29" s="226">
         <f t="shared" si="0"/>
-        <v>311191.98000000004</v>
+        <v>311209.71000000008</v>
       </c>
       <c r="C29" s="91">
         <f>(C12*$B$12+C13*$B$13+C14*$B$14+C15*$B$15+C17*$B$17+C20*$B$20+C16*$B$16+C19*$B$19+C22*$B$22+C23*$B$23+C21*B21)</f>
@@ -42800,7 +42800,7 @@
       </c>
       <c r="AA29" s="91">
         <f t="shared" si="7"/>
-        <v>12406.88</v>
+        <v>12424.61</v>
       </c>
       <c r="AB29" s="91">
         <f t="shared" si="7"/>
@@ -42958,7 +42958,7 @@
       </c>
       <c r="B31" s="226">
         <f t="shared" si="0"/>
-        <v>32363965.920000009</v>
+        <v>32365809.840000011</v>
       </c>
       <c r="C31" s="91">
         <f t="shared" ref="C31:AD31" si="12">C29*104</f>
@@ -43058,7 +43058,7 @@
       </c>
       <c r="AA31" s="91">
         <f t="shared" si="12"/>
-        <v>1290315.52</v>
+        <v>1292159.44</v>
       </c>
       <c r="AB31" s="91">
         <f t="shared" si="12"/>
@@ -43087,7 +43087,7 @@
       </c>
       <c r="B32" s="89">
         <f t="shared" si="0"/>
-        <v>622383.96000000008</v>
+        <v>622419.42000000016</v>
       </c>
       <c r="C32" s="91">
         <f>C29*2</f>
@@ -43187,7 +43187,7 @@
       </c>
       <c r="AA32" s="91">
         <f t="shared" si="15"/>
-        <v>24813.759999999998</v>
+        <v>24849.22</v>
       </c>
       <c r="AB32" s="91">
         <f t="shared" si="15"/>
@@ -43345,7 +43345,7 @@
       </c>
       <c r="B34" s="226">
         <f t="shared" si="0"/>
-        <v>24677524.01400001</v>
+        <v>24678930.00300001</v>
       </c>
       <c r="C34" s="91">
         <f>C29*79.3</f>
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AA34" s="91">
         <f t="shared" si="21"/>
-        <v>983865.58399999992</v>
+        <v>985271.57299999997</v>
       </c>
       <c r="AB34" s="91">
         <f t="shared" si="21"/>
@@ -44849,15 +44849,15 @@
       </c>
       <c r="D28" s="312">
         <f>'KM-Servicio'!$W$179</f>
-        <v>12406.880000000001</v>
+        <v>12420.900000000001</v>
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>269962.10000000003</v>
+        <v>269976.12000000005</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O179</f>
-        <v>96.065660085172283</v>
+        <v>96.174216027874564</v>
       </c>
       <c r="G28" s="314">
         <f>SUM('KM-Servicio'!B179:C179)</f>
@@ -44869,7 +44869,7 @@
       </c>
       <c r="I28" s="312">
         <f>'Oferta Diaria'!AA34</f>
-        <v>983865.58399999992</v>
+        <v>985271.57299999997</v>
       </c>
       <c r="J28" s="161" t="s">
         <v>137</v>
@@ -44895,7 +44895,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>282418.46000000002</v>
+        <v>282432.48000000004</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O186</f>
@@ -44937,7 +44937,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>288887.96000000002</v>
+        <v>288901.98000000004</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O193</f>
@@ -44979,7 +44979,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>293804.78000000003</v>
+        <v>293818.80000000005</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O200</f>
@@ -45021,7 +45021,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>298721.60000000003</v>
+        <v>298735.62000000005</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O207</f>
@@ -45063,7 +45063,7 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>311191.98000000004</v>
+        <v>311206.00000000006</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -45135,15 +45135,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>311191.98000000004</v>
+        <v>311206.00000000006</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>5001534.7400000012</v>
+        <v>5001618.8600000013</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>97.088942456915674</v>
+        <v>97.092560988339088</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="I36" s="169">
         <f>SUM(I4:I34)</f>
-        <v>24677524.01400001</v>
+        <v>24678930.00300001</v>
       </c>
       <c r="J36" s="30"/>
       <c r="K36" s="168"/>
@@ -45187,12 +45187,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="377" t="s">
+      <c r="A3" s="378" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="378"/>
-      <c r="C3" s="378"/>
-      <c r="D3" s="379"/>
+      <c r="B3" s="379"/>
+      <c r="C3" s="379"/>
+      <c r="D3" s="380"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -45338,12 +45338,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="380" t="s">
+      <c r="A13" s="381" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="381"/>
-      <c r="C13" s="381"/>
-      <c r="D13" s="382"/>
+      <c r="B13" s="382"/>
+      <c r="C13" s="382"/>
+      <c r="D13" s="383"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -45390,8 +45390,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="386"/>
-      <c r="H16" s="386"/>
+      <c r="G16" s="377"/>
+      <c r="H16" s="377"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -45406,8 +45406,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="386"/>
-      <c r="H17" s="386"/>
+      <c r="G17" s="377"/>
+      <c r="H17" s="377"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -45422,8 +45422,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="386"/>
-      <c r="H18" s="386"/>
+      <c r="G18" s="377"/>
+      <c r="H18" s="377"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -45437,8 +45437,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="386"/>
-      <c r="H19" s="386"/>
+      <c r="G19" s="377"/>
+      <c r="H19" s="377"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -45452,8 +45452,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="386"/>
-      <c r="H20" s="386"/>
+      <c r="G20" s="377"/>
+      <c r="H20" s="377"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -45467,8 +45467,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="386"/>
-      <c r="H21" s="386"/>
+      <c r="G21" s="377"/>
+      <c r="H21" s="377"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -45493,9 +45493,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="383"/>
-      <c r="C23" s="384"/>
-      <c r="D23" s="385"/>
+      <c r="B23" s="384"/>
+      <c r="C23" s="385"/>
+      <c r="D23" s="386"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -45507,10 +45507,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="380"/>
-      <c r="B24" s="381"/>
-      <c r="C24" s="381"/>
-      <c r="D24" s="382"/>
+      <c r="A24" s="381"/>
+      <c r="B24" s="382"/>
+      <c r="C24" s="382"/>
+      <c r="D24" s="383"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -45623,9 +45623,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="383"/>
-      <c r="C34" s="384"/>
-      <c r="D34" s="385"/>
+      <c r="B34" s="384"/>
+      <c r="C34" s="385"/>
+      <c r="D34" s="386"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -45758,17 +45758,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45776,28 +45776,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -46044,10 +46022,43 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669151E9-FF4A-44C4-A4C1-BC22018F50CD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DF91B3B-11FD-4CE6-AB15-848CF5215DBE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -46064,20 +46075,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DF91B3B-11FD-4CE6-AB15-848CF5215DBE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669151E9-FF4A-44C4-A4C1-BC22018F50CD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/umr/Resumen UMR Junio 2026.xlsx
+++ b/data/umr/Resumen UMR Junio 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{DE6FD30B-F375-45DA-8AE3-7D69E6725542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCDEE732-FFAF-4874-935C-6F439735A4C1}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{DE6FD30B-F375-45DA-8AE3-7D69E6725542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD8BF422-141C-4EEF-A45E-B92DF6C1E01F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4636,28 +4636,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4704,6 +4683,27 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4716,9 +4716,6 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4746,6 +4743,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -15610,14 +15610,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="371" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="351" t="s">
+      <c r="C2" s="371"/>
+      <c r="D2" s="372" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="351"/>
+      <c r="E2" s="372"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -15701,59 +15701,59 @@
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="350" t="s">
+      <c r="B3" s="371" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="350"/>
-      <c r="D3" s="351" t="s">
+      <c r="C3" s="371"/>
+      <c r="D3" s="372" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="351"/>
-      <c r="F3" s="355" t="s">
+      <c r="E3" s="372"/>
+      <c r="F3" s="350" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="355" t="s">
+      <c r="G3" s="350" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="355" t="s">
+      <c r="H3" s="350" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="355" t="s">
+      <c r="I3" s="350" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="355" t="s">
+      <c r="J3" s="350" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="355" t="s">
+      <c r="K3" s="350" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="355" t="s">
+      <c r="L3" s="350" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="355" t="s">
+      <c r="M3" s="350" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="364" t="s">
+      <c r="N3" s="357" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="364" t="s">
+      <c r="O3" s="357" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="363"/>
-      <c r="Q3" s="365" t="s">
+      <c r="P3" s="356"/>
+      <c r="Q3" s="358" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="366"/>
-      <c r="S3" s="367"/>
-      <c r="T3" s="368" t="s">
+      <c r="R3" s="359"/>
+      <c r="S3" s="360"/>
+      <c r="T3" s="361" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="369"/>
-      <c r="V3" s="370"/>
-      <c r="W3" s="361" t="s">
+      <c r="U3" s="362"/>
+      <c r="V3" s="363"/>
+      <c r="W3" s="354" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="361" t="s">
+      <c r="X3" s="354" t="s">
         <v>162</v>
       </c>
     </row>
@@ -15771,17 +15771,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="355"/>
-      <c r="G4" s="358"/>
-      <c r="H4" s="358"/>
-      <c r="I4" s="355"/>
-      <c r="J4" s="355"/>
-      <c r="K4" s="355"/>
-      <c r="L4" s="355"/>
-      <c r="M4" s="355"/>
-      <c r="N4" s="364"/>
-      <c r="O4" s="364"/>
-      <c r="P4" s="363"/>
+      <c r="F4" s="350"/>
+      <c r="G4" s="351"/>
+      <c r="H4" s="351"/>
+      <c r="I4" s="350"/>
+      <c r="J4" s="350"/>
+      <c r="K4" s="350"/>
+      <c r="L4" s="350"/>
+      <c r="M4" s="350"/>
+      <c r="N4" s="357"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="356"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -15800,8 +15800,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="362"/>
-      <c r="X4" s="362"/>
+      <c r="W4" s="355"/>
+      <c r="X4" s="355"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -26278,7 +26278,7 @@
       <c r="O159" s="19"/>
       <c r="P159" s="146"/>
       <c r="Q159" s="183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R159" s="183"/>
       <c r="S159" s="206"/>
@@ -26287,7 +26287,7 @@
       <c r="V159" s="228"/>
       <c r="W159" s="182">
         <f>J159-(Q159*($M$2-$K$1))-(R159*($M$2-$M$1))- (S159*($M$2-$I$2))+ (T159*($G$2))</f>
-        <v>5157.8700000000008</v>
+        <v>5140.1400000000003</v>
       </c>
       <c r="X159" s="182">
         <f>H159*$M$2</f>
@@ -26415,7 +26415,7 @@
       <c r="O161" s="19"/>
       <c r="P161" s="146"/>
       <c r="Q161" s="183">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R161" s="187"/>
       <c r="S161" s="207"/>
@@ -26424,7 +26424,7 @@
       <c r="V161" s="189"/>
       <c r="W161" s="182">
         <f>J161-(Q161*($M$1-$K$1))</f>
-        <v>1120.45</v>
+        <v>1124.1599999999999</v>
       </c>
       <c r="X161" s="182">
         <f>H161*$M$1</f>
@@ -26679,7 +26679,7 @@
       </c>
       <c r="O165" s="21">
         <f>(W165/N165)*100</f>
-        <v>96.34939296142619</v>
+        <v>96.24166282465039</v>
       </c>
       <c r="P165" s="192"/>
       <c r="Q165" s="181"/>
@@ -26690,7 +26690,7 @@
       <c r="V165" s="181"/>
       <c r="W165" s="193">
         <f>SUM(W159:W164)</f>
-        <v>12538.910000000003</v>
+        <v>12524.890000000001</v>
       </c>
       <c r="X165" s="193">
         <f>SUM(X159:X164)</f>
@@ -30467,38 +30467,38 @@
     <row r="222" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="223" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223"/>
-      <c r="B223" s="352" t="s">
+      <c r="B223" s="366" t="s">
         <v>56</v>
       </c>
-      <c r="C223" s="353"/>
-      <c r="D223" s="353"/>
-      <c r="E223" s="353"/>
-      <c r="F223" s="353"/>
-      <c r="G223" s="354"/>
+      <c r="C223" s="367"/>
+      <c r="D223" s="367"/>
+      <c r="E223" s="367"/>
+      <c r="F223" s="367"/>
+      <c r="G223" s="368"/>
       <c r="H223" s="290"/>
-      <c r="I223" s="352" t="s">
+      <c r="I223" s="366" t="s">
         <v>57</v>
       </c>
-      <c r="J223" s="353"/>
-      <c r="K223" s="353"/>
-      <c r="L223" s="353"/>
-      <c r="M223" s="353"/>
-      <c r="N223" s="354"/>
-      <c r="P223" s="371" t="s">
+      <c r="J223" s="367"/>
+      <c r="K223" s="367"/>
+      <c r="L223" s="367"/>
+      <c r="M223" s="367"/>
+      <c r="N223" s="368"/>
+      <c r="P223" s="364" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="371"/>
-      <c r="R223" s="371"/>
-      <c r="S223" s="372"/>
-      <c r="T223" s="368" t="s">
+      <c r="Q223" s="364"/>
+      <c r="R223" s="364"/>
+      <c r="S223" s="365"/>
+      <c r="T223" s="361" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="369"/>
-      <c r="V223" s="370"/>
-      <c r="W223" s="359" t="s">
+      <c r="U223" s="362"/>
+      <c r="V223" s="363"/>
+      <c r="W223" s="352" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="359" t="s">
+      <c r="X223" s="352" t="s">
         <v>162</v>
       </c>
     </row>
@@ -30564,8 +30564,8 @@
       <c r="V224" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="360"/>
-      <c r="X224" s="360"/>
+      <c r="W224" s="353"/>
+      <c r="X224" s="353"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -30623,7 +30623,7 @@
       <c r="O225" s="124"/>
       <c r="P225" s="209">
         <f>SUM(Q194,Q187,Q180,Q173,Q166,Q159,Q152,Q145,Q138,Q131,Q124,Q117,Q110,Q103,Q96,Q89,Q82,Q75,Q68,Q61,Q54,Q47,Q40,Q33,Q26,Q19,Q12,Q5,Q201,Q208,Q215)</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q225" s="209">
         <f>SUM(R194,R187,R180,R173,R166,R159,R152,R145,R138,R131,R124,R117,R110,R103,R96,R89,R82,R75,R68,R61,R54,R47,R40,R33,R26,R19,R12,R5,R201,R208,R215)</f>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="W225" s="231">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214</f>
-        <v>311206.00000000006</v>
+        <v>311191.9800000001</v>
       </c>
       <c r="X225" s="231">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214</f>
@@ -31075,10 +31075,10 @@
     </row>
     <row r="235" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A235" s="24"/>
-      <c r="B235" s="356" t="s">
+      <c r="B235" s="369" t="s">
         <v>55</v>
       </c>
-      <c r="C235" s="357"/>
+      <c r="C235" s="370"/>
       <c r="D235" s="25" t="s">
         <v>65</v>
       </c>
@@ -31254,6 +31254,18 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="28">
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="I223:N223"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B235:C235"/>
+    <mergeCell ref="B223:G223"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
     <mergeCell ref="A83:A86"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
@@ -31270,18 +31282,6 @@
     <mergeCell ref="P223:S223"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
-    <mergeCell ref="I223:N223"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="B235:C235"/>
-    <mergeCell ref="B223:G223"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="D187:E192 D180:E185 D173:E178 D194:E199">
     <cfRule type="expression" dxfId="46" priority="174">
@@ -40049,6 +40049,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -40065,21 +40080,6 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -41898,7 +41898,7 @@
       </c>
       <c r="Y19" s="83">
         <f>'KM-Servicio'!Q159</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z19" s="83">
         <f>'KM-Servicio'!Q166</f>
@@ -42700,7 +42700,7 @@
       </c>
       <c r="B29" s="226">
         <f t="shared" si="0"/>
-        <v>311209.71000000008</v>
+        <v>311191.98000000004</v>
       </c>
       <c r="C29" s="91">
         <f>(C12*$B$12+C13*$B$13+C14*$B$14+C15*$B$15+C17*$B$17+C20*$B$20+C16*$B$16+C19*$B$19+C22*$B$22+C23*$B$23+C21*B21)</f>
@@ -42792,7 +42792,7 @@
       </c>
       <c r="Y29" s="91">
         <f t="shared" si="7"/>
-        <v>12538.910000000003</v>
+        <v>12521.180000000004</v>
       </c>
       <c r="Z29" s="91">
         <f t="shared" si="7"/>
@@ -42958,7 +42958,7 @@
       </c>
       <c r="B31" s="226">
         <f t="shared" si="0"/>
-        <v>32365809.840000011</v>
+        <v>32363965.920000009</v>
       </c>
       <c r="C31" s="91">
         <f t="shared" ref="C31:AD31" si="12">C29*104</f>
@@ -43050,7 +43050,7 @@
       </c>
       <c r="Y31" s="91">
         <f t="shared" si="12"/>
-        <v>1304046.6400000004</v>
+        <v>1302202.7200000004</v>
       </c>
       <c r="Z31" s="91">
         <f t="shared" si="12"/>
@@ -43087,7 +43087,7 @@
       </c>
       <c r="B32" s="89">
         <f t="shared" si="0"/>
-        <v>622419.42000000016</v>
+        <v>622383.96000000008</v>
       </c>
       <c r="C32" s="91">
         <f>C29*2</f>
@@ -43179,7 +43179,7 @@
       </c>
       <c r="Y32" s="91">
         <f t="shared" si="15"/>
-        <v>25077.820000000007</v>
+        <v>25042.360000000008</v>
       </c>
       <c r="Z32" s="91">
         <f t="shared" si="15"/>
@@ -43345,7 +43345,7 @@
       </c>
       <c r="B34" s="226">
         <f t="shared" si="0"/>
-        <v>24678930.00300001</v>
+        <v>24677524.01400001</v>
       </c>
       <c r="C34" s="91">
         <f>C29*79.3</f>
@@ -43437,7 +43437,7 @@
       </c>
       <c r="Y34" s="91">
         <f t="shared" si="21"/>
-        <v>994335.5630000002</v>
+        <v>992929.57400000026</v>
       </c>
       <c r="Z34" s="91">
         <f t="shared" si="21"/>
@@ -44765,15 +44765,15 @@
       </c>
       <c r="D26" s="12">
         <f>'KM-Servicio'!$W$165</f>
-        <v>12538.910000000003</v>
+        <v>12524.890000000001</v>
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>245171.10000000006</v>
+        <v>245157.08000000007</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O165</f>
-        <v>96.34939296142619</v>
+        <v>96.24166282465039</v>
       </c>
       <c r="G26" s="167">
         <f>SUM('KM-Servicio'!B165:C165)</f>
@@ -44785,7 +44785,7 @@
       </c>
       <c r="I26" s="12">
         <f>'Oferta Diaria'!Y34</f>
-        <v>994335.5630000002</v>
+        <v>992929.57400000026</v>
       </c>
       <c r="J26" s="161" t="s">
         <v>137</v>
@@ -44811,7 +44811,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>257555.22000000006</v>
+        <v>257541.20000000007</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O172</f>
@@ -44853,7 +44853,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>269976.12000000005</v>
+        <v>269962.10000000009</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O179</f>
@@ -44895,7 +44895,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>282432.48000000004</v>
+        <v>282418.46000000008</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O186</f>
@@ -44937,7 +44937,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>288901.98000000004</v>
+        <v>288887.96000000008</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O193</f>
@@ -44979,7 +44979,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>293818.80000000005</v>
+        <v>293804.78000000009</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O200</f>
@@ -45021,7 +45021,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>298735.62000000005</v>
+        <v>298721.60000000009</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O207</f>
@@ -45063,7 +45063,7 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>311206.00000000006</v>
+        <v>311191.9800000001</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -45135,15 +45135,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>311206.00000000006</v>
+        <v>311191.9800000001</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>5001618.8600000013</v>
+        <v>5001506.7000000011</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>97.092560988339088</v>
+        <v>97.088969983779904</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="I36" s="169">
         <f>SUM(I4:I34)</f>
-        <v>24678930.00300001</v>
+        <v>24677524.01400001</v>
       </c>
       <c r="J36" s="30"/>
       <c r="K36" s="168"/>
@@ -45187,12 +45187,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="378" t="s">
+      <c r="A3" s="377" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="379"/>
-      <c r="C3" s="379"/>
-      <c r="D3" s="380"/>
+      <c r="B3" s="378"/>
+      <c r="C3" s="378"/>
+      <c r="D3" s="379"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -45338,12 +45338,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="381" t="s">
+      <c r="A13" s="380" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="382"/>
-      <c r="C13" s="382"/>
-      <c r="D13" s="383"/>
+      <c r="B13" s="381"/>
+      <c r="C13" s="381"/>
+      <c r="D13" s="382"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -45390,8 +45390,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="377"/>
-      <c r="H16" s="377"/>
+      <c r="G16" s="386"/>
+      <c r="H16" s="386"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -45406,8 +45406,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="377"/>
-      <c r="H17" s="377"/>
+      <c r="G17" s="386"/>
+      <c r="H17" s="386"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -45422,8 +45422,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="377"/>
-      <c r="H18" s="377"/>
+      <c r="G18" s="386"/>
+      <c r="H18" s="386"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -45437,8 +45437,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="377"/>
-      <c r="H19" s="377"/>
+      <c r="G19" s="386"/>
+      <c r="H19" s="386"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -45452,8 +45452,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="377"/>
-      <c r="H20" s="377"/>
+      <c r="G20" s="386"/>
+      <c r="H20" s="386"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -45467,8 +45467,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="377"/>
-      <c r="H21" s="377"/>
+      <c r="G21" s="386"/>
+      <c r="H21" s="386"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -45493,9 +45493,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="384"/>
-      <c r="C23" s="385"/>
-      <c r="D23" s="386"/>
+      <c r="B23" s="383"/>
+      <c r="C23" s="384"/>
+      <c r="D23" s="385"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -45507,10 +45507,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="381"/>
-      <c r="B24" s="382"/>
-      <c r="C24" s="382"/>
-      <c r="D24" s="383"/>
+      <c r="A24" s="380"/>
+      <c r="B24" s="381"/>
+      <c r="C24" s="381"/>
+      <c r="D24" s="382"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -45623,9 +45623,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="384"/>
-      <c r="C34" s="385"/>
-      <c r="D34" s="386"/>
+      <c r="B34" s="383"/>
+      <c r="C34" s="384"/>
+      <c r="D34" s="385"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -45758,17 +45758,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45776,6 +45776,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -46022,29 +46044,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669151E9-FF4A-44C4-A4C1-BC22018F50CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE50111-D01F-48FD-ADC2-456C6B7A1B05}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DF91B3B-11FD-4CE6-AB15-848CF5215DBE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -46061,23 +46080,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE50111-D01F-48FD-ADC2-456C6B7A1B05}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669151E9-FF4A-44C4-A4C1-BC22018F50CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>